--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1317,6 +1317,7221 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125584011</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528024</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7059858</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125583991</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527969</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7059849</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125584025</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>528024</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7059858</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125598574</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>528019</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7059825</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125598451</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527552</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7059543</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125598449</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>528035</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7059829</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125598510</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>528087</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7059873</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125598509</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>528048</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7059876</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125598555</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>527519</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7059395</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125598498</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>527595</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7059511</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125598575</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>527482</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7059430</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125598459</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>527589</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7059511</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125598497</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>527567</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7059440</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125598467</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>527570</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7059603</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125598448</v>
+      </c>
+      <c r="B21" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>528190</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7059902</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125598522</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>527884</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7059787</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125598520</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>527925</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7059867</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125598466</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>527759</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7059678</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125598496</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>527610</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7059504</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125598511</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>527884</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7059785</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125598500</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>527614</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7059597</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125598465</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>528141</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7059905</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125598488</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>527940</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7059824</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125598515</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>527817</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7059737</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125598494</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>527890</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7059744</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125598499</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>527590</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7059608</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack &lt;5år</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125598495</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>527871</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7059714</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125598566</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91424</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>65</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>527975</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7059791</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125598553</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>527930</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7059833</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125598556</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>527522</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7059566</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125598534</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>527702</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7059650</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125598561</v>
+      </c>
+      <c r="B38" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>527520</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7059331</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125598557</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>527560</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7059635</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125598492</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>527904</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7059740</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125598452</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>527573</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7059652</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125598521</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>527890</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7059852</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125598554</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>527561</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7059318</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125598502</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>527602</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7059578</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125598528</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80900</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>527479</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7059420</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125598543</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91326</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>527509</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7059455</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125598493</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>527891</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7059742</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125598458</v>
+      </c>
+      <c r="B48" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>53</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>527539</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7059464</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125598455</v>
+      </c>
+      <c r="B49" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>53</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>527827</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7059738</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125598519</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92646</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>527841</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7059750</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125598491</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>527835</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7059763</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125598576</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75017</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>308</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>527583</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7059611</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125598525</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>527496</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7059466</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125598468</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>527542</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7059620</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125598562</v>
+      </c>
+      <c r="B55" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>527573</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7059654</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125598487</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>528055</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7059900</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125598490</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>527864</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7059796</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125598461</v>
+      </c>
+      <c r="B58" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>53</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>527527</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7059604</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125598457</v>
+      </c>
+      <c r="B59" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>53</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>527542</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7059349</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125598482</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>527578</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7059506</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125598475</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>528015</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7059826</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125598526</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>527563</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7059540</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125598536</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>527559</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7059578</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125598460</v>
+      </c>
+      <c r="B64" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>53</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>527527</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7059584</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125598489</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>527850</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7059804</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125598456</v>
+      </c>
+      <c r="B66" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>53</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>527574</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7059456</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125598450</v>
+      </c>
+      <c r="B67" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>527522</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7059339</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125598476</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>527488</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7059420</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125598481</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>527880</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7059774</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125598516</v>
+      </c>
+      <c r="B70" t="n">
+        <v>74836</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>527519</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7059332</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125598537</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91326</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>528146</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7059953</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125598512</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>527496</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7059466</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125598545</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91326</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>527569</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7059499</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125598579</v>
+      </c>
+      <c r="B74" t="n">
+        <v>77874</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>527524</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7059550</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125598454</v>
+      </c>
+      <c r="B75" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>528167</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7059940</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125598535</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Småvattenån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>527536</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7059461</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1320,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125584011</v>
+        <v>125584025</v>
       </c>
       <c r="B7" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125584025</v>
+        <v>125584011</v>
       </c>
       <c r="B9" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125598574</v>
+        <v>125598493</v>
       </c>
       <c r="B10" t="n">
-        <v>92448</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,25 +1638,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528019</v>
+        <v>527891</v>
       </c>
       <c r="R10" t="n">
-        <v>7059825</v>
+        <v>7059742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,6 +1702,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125598451</v>
+        <v>125598557</v>
       </c>
       <c r="B11" t="n">
-        <v>75025</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1749,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527552</v>
+        <v>527560</v>
       </c>
       <c r="R11" t="n">
-        <v>7059543</v>
+        <v>7059635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125598449</v>
+        <v>125598461</v>
       </c>
       <c r="B12" t="n">
-        <v>75025</v>
+        <v>96522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1851,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528035</v>
+        <v>527527</v>
       </c>
       <c r="R12" t="n">
-        <v>7059829</v>
+        <v>7059604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125598510</v>
+        <v>125598459</v>
       </c>
       <c r="B13" t="n">
-        <v>80029</v>
+        <v>96522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528087</v>
+        <v>527589</v>
       </c>
       <c r="R13" t="n">
-        <v>7059873</v>
+        <v>7059511</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598509</v>
+        <v>125598511</v>
       </c>
       <c r="B14" t="n">
         <v>80029</v>
@@ -2074,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528048</v>
+        <v>527884</v>
       </c>
       <c r="R14" t="n">
-        <v>7059876</v>
+        <v>7059785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598555</v>
+        <v>125598457</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2157,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527519</v>
+        <v>527542</v>
       </c>
       <c r="R15" t="n">
-        <v>7059395</v>
+        <v>7059349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598498</v>
+        <v>125598491</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527595</v>
+        <v>527835</v>
       </c>
       <c r="R16" t="n">
-        <v>7059511</v>
+        <v>7059763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2323,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598575</v>
+        <v>125598456</v>
       </c>
       <c r="B17" t="n">
-        <v>92448</v>
+        <v>96522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527482</v>
+        <v>527574</v>
       </c>
       <c r="R17" t="n">
-        <v>7059430</v>
+        <v>7059456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598459</v>
+        <v>125598515</v>
       </c>
       <c r="B18" t="n">
-        <v>96522</v>
+        <v>79932</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527589</v>
+        <v>527817</v>
       </c>
       <c r="R18" t="n">
-        <v>7059511</v>
+        <v>7059737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2554,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125598497</v>
+        <v>125598490</v>
       </c>
       <c r="B19" t="n">
         <v>57635</v>
@@ -2589,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527567</v>
+        <v>527864</v>
       </c>
       <c r="R19" t="n">
-        <v>7059440</v>
+        <v>7059796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,10 +2661,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598467</v>
+        <v>125598554</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,21 +2677,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527570</v>
+        <v>527561</v>
       </c>
       <c r="R20" t="n">
-        <v>7059603</v>
+        <v>7059318</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,10 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598448</v>
+        <v>125598487</v>
       </c>
       <c r="B21" t="n">
-        <v>75025</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2779,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528190</v>
+        <v>528055</v>
       </c>
       <c r="R21" t="n">
-        <v>7059902</v>
+        <v>7059900</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,6 +2839,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598522</v>
+        <v>125598562</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>82737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2886,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2910,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527884</v>
+        <v>527573</v>
       </c>
       <c r="R22" t="n">
-        <v>7059787</v>
+        <v>7059654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,10 +2972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598520</v>
+        <v>125598521</v>
       </c>
       <c r="B23" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,21 +2988,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527925</v>
+        <v>527890</v>
       </c>
       <c r="R23" t="n">
-        <v>7059867</v>
+        <v>7059852</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598466</v>
+        <v>125598525</v>
       </c>
       <c r="B24" t="n">
-        <v>79565</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527759</v>
+        <v>527496</v>
       </c>
       <c r="R24" t="n">
-        <v>7059678</v>
+        <v>7059466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598496</v>
+        <v>125598475</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>79536</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527610</v>
+        <v>528015</v>
       </c>
       <c r="R25" t="n">
-        <v>7059504</v>
+        <v>7059826</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,11 +3252,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598511</v>
+        <v>125598488</v>
       </c>
       <c r="B26" t="n">
-        <v>80029</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,21 +3294,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527884</v>
+        <v>527940</v>
       </c>
       <c r="R26" t="n">
-        <v>7059785</v>
+        <v>7059824</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,6 +3354,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598500</v>
+        <v>125598555</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,21 +3401,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3415,10 +3425,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527614</v>
+        <v>527519</v>
       </c>
       <c r="R27" t="n">
-        <v>7059597</v>
+        <v>7059395</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,11 +3461,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3487,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598465</v>
+        <v>125598509</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>80029</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,21 +3503,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3522,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528141</v>
+        <v>528048</v>
       </c>
       <c r="R28" t="n">
-        <v>7059905</v>
+        <v>7059876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598488</v>
+        <v>125598528</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
+        <v>80900</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3600,21 +3605,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527940</v>
+        <v>527479</v>
       </c>
       <c r="R29" t="n">
-        <v>7059824</v>
+        <v>7059420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3660,11 +3665,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598515</v>
+        <v>125598449</v>
       </c>
       <c r="B30" t="n">
-        <v>79932</v>
+        <v>75025</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3703,25 +3703,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527817</v>
+        <v>528035</v>
       </c>
       <c r="R30" t="n">
-        <v>7059737</v>
+        <v>7059829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598494</v>
+        <v>125598536</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>78683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527890</v>
+        <v>527559</v>
       </c>
       <c r="R31" t="n">
-        <v>7059744</v>
+        <v>7059578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,11 +3869,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,7 +3895,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598499</v>
+        <v>125598495</v>
       </c>
       <c r="B32" t="n">
         <v>57635</v>
@@ -3940,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527590</v>
+        <v>527871</v>
       </c>
       <c r="R32" t="n">
-        <v>7059608</v>
+        <v>7059714</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3980,7 +3975,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack &lt;5år</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4007,10 +4002,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598495</v>
+        <v>125598476</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
+        <v>79536</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4023,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527871</v>
+        <v>527488</v>
       </c>
       <c r="R33" t="n">
-        <v>7059714</v>
+        <v>7059420</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,11 +4078,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4114,10 +4104,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598566</v>
+        <v>125598460</v>
       </c>
       <c r="B34" t="n">
-        <v>91424</v>
+        <v>96522</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4126,25 +4116,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4144,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527975</v>
+        <v>527527</v>
       </c>
       <c r="R34" t="n">
-        <v>7059791</v>
+        <v>7059584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598553</v>
+        <v>125598455</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4232,21 +4222,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4256,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527930</v>
+        <v>527827</v>
       </c>
       <c r="R35" t="n">
-        <v>7059833</v>
+        <v>7059738</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4420,10 +4410,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598534</v>
+        <v>125598492</v>
       </c>
       <c r="B37" t="n">
-        <v>78683</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4436,21 +4426,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4460,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527702</v>
+        <v>527904</v>
       </c>
       <c r="R37" t="n">
-        <v>7059650</v>
+        <v>7059740</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4496,6 +4486,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4522,10 +4517,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598561</v>
+        <v>125598520</v>
       </c>
       <c r="B38" t="n">
-        <v>82737</v>
+        <v>78684</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4538,21 +4533,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527520</v>
+        <v>527925</v>
       </c>
       <c r="R38" t="n">
-        <v>7059331</v>
+        <v>7059867</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4624,10 +4619,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598557</v>
+        <v>125598499</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4640,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4664,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527560</v>
+        <v>527590</v>
       </c>
       <c r="R39" t="n">
-        <v>7059635</v>
+        <v>7059608</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4700,6 +4695,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack &lt;5år</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4726,7 +4726,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598492</v>
+        <v>125598496</v>
       </c>
       <c r="B40" t="n">
         <v>57635</v>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527904</v>
+        <v>527610</v>
       </c>
       <c r="R40" t="n">
-        <v>7059740</v>
+        <v>7059504</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4833,10 +4833,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598452</v>
+        <v>125598510</v>
       </c>
       <c r="B41" t="n">
-        <v>75025</v>
+        <v>80029</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527573</v>
+        <v>528087</v>
       </c>
       <c r="R41" t="n">
-        <v>7059652</v>
+        <v>7059873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4935,10 +4935,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598521</v>
+        <v>125598450</v>
       </c>
       <c r="B42" t="n">
-        <v>80028</v>
+        <v>75025</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4951,21 +4951,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527890</v>
+        <v>527522</v>
       </c>
       <c r="R42" t="n">
-        <v>7059852</v>
+        <v>7059339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5037,10 +5037,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598554</v>
+        <v>125598468</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5053,21 +5053,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527561</v>
+        <v>527542</v>
       </c>
       <c r="R43" t="n">
-        <v>7059318</v>
+        <v>7059620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598502</v>
+        <v>125598566</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>91424</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5151,25 +5151,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527602</v>
+        <v>527975</v>
       </c>
       <c r="R44" t="n">
-        <v>7059578</v>
+        <v>7059791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5215,11 +5215,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5246,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598528</v>
+        <v>125598545</v>
       </c>
       <c r="B45" t="n">
-        <v>80900</v>
+        <v>91326</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5258,25 +5253,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527479</v>
+        <v>527569</v>
       </c>
       <c r="R45" t="n">
-        <v>7059420</v>
+        <v>7059499</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5348,10 +5343,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598543</v>
+        <v>125598500</v>
       </c>
       <c r="B46" t="n">
-        <v>91326</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5360,25 +5355,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527509</v>
+        <v>527614</v>
       </c>
       <c r="R46" t="n">
-        <v>7059455</v>
+        <v>7059597</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,6 +5419,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5450,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598493</v>
+        <v>125598451</v>
       </c>
       <c r="B47" t="n">
-        <v>57635</v>
+        <v>75025</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527891</v>
+        <v>527552</v>
       </c>
       <c r="R47" t="n">
-        <v>7059742</v>
+        <v>7059543</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,11 +5526,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5557,10 +5552,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598458</v>
+        <v>125598502</v>
       </c>
       <c r="B48" t="n">
-        <v>96522</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5573,21 +5568,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527539</v>
+        <v>527602</v>
       </c>
       <c r="R48" t="n">
-        <v>7059464</v>
+        <v>7059578</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,6 +5628,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125598455</v>
+        <v>125598575</v>
       </c>
       <c r="B49" t="n">
-        <v>96522</v>
+        <v>92448</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,25 +5671,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527827</v>
+        <v>527482</v>
       </c>
       <c r="R49" t="n">
-        <v>7059738</v>
+        <v>7059430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598519</v>
+        <v>125598561</v>
       </c>
       <c r="B50" t="n">
-        <v>92646</v>
+        <v>82737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5777,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527841</v>
+        <v>527520</v>
       </c>
       <c r="R50" t="n">
-        <v>7059750</v>
+        <v>7059331</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5863,10 +5863,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598491</v>
+        <v>125598574</v>
       </c>
       <c r="B51" t="n">
-        <v>57635</v>
+        <v>92448</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5875,25 +5875,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527835</v>
+        <v>528019</v>
       </c>
       <c r="R51" t="n">
-        <v>7059763</v>
+        <v>7059825</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5939,11 +5939,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,10 +5965,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598576</v>
+        <v>125598481</v>
       </c>
       <c r="B52" t="n">
-        <v>75017</v>
+        <v>91166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5981,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6005,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527583</v>
+        <v>527880</v>
       </c>
       <c r="R52" t="n">
-        <v>7059611</v>
+        <v>7059774</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6072,10 +6067,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125598525</v>
+        <v>125598452</v>
       </c>
       <c r="B53" t="n">
-        <v>80028</v>
+        <v>75025</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6088,21 +6083,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527496</v>
+        <v>527573</v>
       </c>
       <c r="R53" t="n">
-        <v>7059466</v>
+        <v>7059652</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6174,10 +6169,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598468</v>
+        <v>125598516</v>
       </c>
       <c r="B54" t="n">
-        <v>79565</v>
+        <v>74836</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6186,25 +6181,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6428</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6214,10 +6209,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527542</v>
+        <v>527519</v>
       </c>
       <c r="R54" t="n">
-        <v>7059620</v>
+        <v>7059332</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6276,10 +6271,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598562</v>
+        <v>125598526</v>
       </c>
       <c r="B55" t="n">
-        <v>82737</v>
+        <v>80028</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6292,21 +6287,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6316,10 +6311,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527573</v>
+        <v>527563</v>
       </c>
       <c r="R55" t="n">
-        <v>7059654</v>
+        <v>7059540</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6378,10 +6373,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598487</v>
+        <v>125598482</v>
       </c>
       <c r="B56" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6394,21 +6389,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6418,10 +6413,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528055</v>
+        <v>527578</v>
       </c>
       <c r="R56" t="n">
-        <v>7059900</v>
+        <v>7059506</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6454,11 +6449,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6485,10 +6475,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598490</v>
+        <v>125598543</v>
       </c>
       <c r="B57" t="n">
-        <v>57635</v>
+        <v>91326</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6497,25 +6487,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6525,10 +6515,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527864</v>
+        <v>527509</v>
       </c>
       <c r="R57" t="n">
-        <v>7059796</v>
+        <v>7059455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6561,11 +6551,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,10 +6577,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598461</v>
+        <v>125598537</v>
       </c>
       <c r="B58" t="n">
-        <v>96522</v>
+        <v>91326</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6604,25 +6589,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6632,10 +6617,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527527</v>
+        <v>528146</v>
       </c>
       <c r="R58" t="n">
-        <v>7059604</v>
+        <v>7059953</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6694,10 +6679,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598457</v>
+        <v>125598489</v>
       </c>
       <c r="B59" t="n">
-        <v>96522</v>
+        <v>57635</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6710,21 +6695,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6734,10 +6719,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527542</v>
+        <v>527850</v>
       </c>
       <c r="R59" t="n">
-        <v>7059349</v>
+        <v>7059804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6770,6 +6755,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6796,10 +6786,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598482</v>
+        <v>125598498</v>
       </c>
       <c r="B60" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6812,21 +6802,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6836,10 +6826,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527578</v>
+        <v>527595</v>
       </c>
       <c r="R60" t="n">
-        <v>7059506</v>
+        <v>7059511</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6872,6 +6862,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6898,10 +6893,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598475</v>
+        <v>125598576</v>
       </c>
       <c r="B61" t="n">
-        <v>79536</v>
+        <v>75017</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,21 +6909,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6938,10 +6933,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>528015</v>
+        <v>527583</v>
       </c>
       <c r="R61" t="n">
-        <v>7059826</v>
+        <v>7059611</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7000,10 +6995,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125598526</v>
+        <v>125598466</v>
       </c>
       <c r="B62" t="n">
-        <v>80028</v>
+        <v>79565</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7016,21 +7011,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7040,10 +7035,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527563</v>
+        <v>527759</v>
       </c>
       <c r="R62" t="n">
-        <v>7059540</v>
+        <v>7059678</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7102,10 +7097,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125598536</v>
+        <v>125598512</v>
       </c>
       <c r="B63" t="n">
-        <v>78683</v>
+        <v>80029</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7118,21 +7113,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7142,10 +7137,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527559</v>
+        <v>527496</v>
       </c>
       <c r="R63" t="n">
-        <v>7059578</v>
+        <v>7059466</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7204,7 +7199,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125598460</v>
+        <v>125598454</v>
       </c>
       <c r="B64" t="n">
         <v>96522</v>
@@ -7244,10 +7239,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527527</v>
+        <v>528167</v>
       </c>
       <c r="R64" t="n">
-        <v>7059584</v>
+        <v>7059940</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7306,7 +7301,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125598489</v>
+        <v>125598497</v>
       </c>
       <c r="B65" t="n">
         <v>57635</v>
@@ -7346,10 +7341,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527850</v>
+        <v>527567</v>
       </c>
       <c r="R65" t="n">
-        <v>7059804</v>
+        <v>7059440</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7413,10 +7408,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125598456</v>
+        <v>125598553</v>
       </c>
       <c r="B66" t="n">
-        <v>96522</v>
+        <v>78947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7429,21 +7424,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7453,10 +7448,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527574</v>
+        <v>527930</v>
       </c>
       <c r="R66" t="n">
-        <v>7059456</v>
+        <v>7059833</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7515,10 +7510,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125598450</v>
+        <v>125598535</v>
       </c>
       <c r="B67" t="n">
-        <v>75025</v>
+        <v>78683</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7531,21 +7526,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7555,10 +7550,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527522</v>
+        <v>527536</v>
       </c>
       <c r="R67" t="n">
-        <v>7059339</v>
+        <v>7059461</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7617,10 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125598476</v>
+        <v>125598467</v>
       </c>
       <c r="B68" t="n">
-        <v>79536</v>
+        <v>79565</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7633,21 +7628,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7657,10 +7652,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527488</v>
+        <v>527570</v>
       </c>
       <c r="R68" t="n">
-        <v>7059420</v>
+        <v>7059603</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7719,10 +7714,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125598481</v>
+        <v>125598494</v>
       </c>
       <c r="B69" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7735,21 +7730,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7759,10 +7754,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527880</v>
+        <v>527890</v>
       </c>
       <c r="R69" t="n">
-        <v>7059774</v>
+        <v>7059744</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7795,6 +7790,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7821,10 +7821,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125598516</v>
+        <v>125598522</v>
       </c>
       <c r="B70" t="n">
-        <v>74836</v>
+        <v>80028</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7833,25 +7833,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527519</v>
+        <v>527884</v>
       </c>
       <c r="R70" t="n">
-        <v>7059332</v>
+        <v>7059787</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7923,10 +7923,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125598537</v>
+        <v>125598519</v>
       </c>
       <c r="B71" t="n">
-        <v>91326</v>
+        <v>92646</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7935,25 +7935,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>528146</v>
+        <v>527841</v>
       </c>
       <c r="R71" t="n">
-        <v>7059953</v>
+        <v>7059750</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125598512</v>
+        <v>125598534</v>
       </c>
       <c r="B72" t="n">
-        <v>80029</v>
+        <v>78683</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8041,21 +8041,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527496</v>
+        <v>527702</v>
       </c>
       <c r="R72" t="n">
-        <v>7059466</v>
+        <v>7059650</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8127,10 +8127,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125598545</v>
+        <v>125598458</v>
       </c>
       <c r="B73" t="n">
-        <v>91326</v>
+        <v>96522</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8139,25 +8139,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527569</v>
+        <v>527539</v>
       </c>
       <c r="R73" t="n">
-        <v>7059499</v>
+        <v>7059464</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8229,10 +8229,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125598579</v>
+        <v>125598448</v>
       </c>
       <c r="B74" t="n">
-        <v>77874</v>
+        <v>75025</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8245,21 +8245,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8269,10 +8269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527524</v>
+        <v>528190</v>
       </c>
       <c r="R74" t="n">
-        <v>7059550</v>
+        <v>7059902</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8331,10 +8331,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125598454</v>
+        <v>125598465</v>
       </c>
       <c r="B75" t="n">
-        <v>96522</v>
+        <v>79565</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>528167</v>
+        <v>528141</v>
       </c>
       <c r="R75" t="n">
-        <v>7059940</v>
+        <v>7059905</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125598535</v>
+        <v>125598579</v>
       </c>
       <c r="B76" t="n">
-        <v>78683</v>
+        <v>77874</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8449,21 +8449,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527536</v>
+        <v>527524</v>
       </c>
       <c r="R76" t="n">
-        <v>7059461</v>
+        <v>7059550</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598545</v>
+        <v>125598460</v>
       </c>
       <c r="B17" t="n">
-        <v>91380</v>
+        <v>96577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527569</v>
+        <v>527527</v>
       </c>
       <c r="R17" t="n">
-        <v>7059499</v>
+        <v>7059584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598460</v>
+        <v>125598545</v>
       </c>
       <c r="B18" t="n">
-        <v>96577</v>
+        <v>91380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527527</v>
+        <v>527569</v>
       </c>
       <c r="R18" t="n">
-        <v>7059584</v>
+        <v>7059499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598454</v>
+        <v>125598475</v>
       </c>
       <c r="B40" t="n">
-        <v>96577</v>
+        <v>79556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528167</v>
+        <v>528015</v>
       </c>
       <c r="R40" t="n">
-        <v>7059940</v>
+        <v>7059826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,32 +4618,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598566</v>
+        <v>125598454</v>
       </c>
       <c r="B41" t="n">
-        <v>91478</v>
+        <v>96577</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527975</v>
+        <v>528167</v>
       </c>
       <c r="R41" t="n">
-        <v>7059791</v>
+        <v>7059940</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598475</v>
+        <v>125598566</v>
       </c>
       <c r="B42" t="n">
-        <v>79556</v>
+        <v>91478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528015</v>
+        <v>527975</v>
       </c>
       <c r="R42" t="n">
-        <v>7059826</v>
+        <v>7059791</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598455</v>
+        <v>125598520</v>
       </c>
       <c r="B50" t="n">
-        <v>96577</v>
+        <v>78726</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527827</v>
+        <v>527925</v>
       </c>
       <c r="R50" t="n">
-        <v>7059738</v>
+        <v>7059867</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598509</v>
+        <v>125598455</v>
       </c>
       <c r="B51" t="n">
-        <v>80071</v>
+        <v>96577</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528048</v>
+        <v>527827</v>
       </c>
       <c r="R51" t="n">
-        <v>7059876</v>
+        <v>7059738</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B52" t="n">
-        <v>78726</v>
+        <v>80071</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R52" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>125598519</v>
       </c>
       <c r="B12" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598459</v>
+        <v>125598537</v>
       </c>
       <c r="B15" t="n">
-        <v>96577</v>
+        <v>91387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527589</v>
+        <v>528146</v>
       </c>
       <c r="R15" t="n">
-        <v>7059511</v>
+        <v>7059953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598537</v>
+        <v>125598459</v>
       </c>
       <c r="B16" t="n">
-        <v>91380</v>
+        <v>96584</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528146</v>
+        <v>527589</v>
       </c>
       <c r="R16" t="n">
-        <v>7059953</v>
+        <v>7059511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>125598460</v>
       </c>
       <c r="B17" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>125598545</v>
       </c>
       <c r="B18" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598562</v>
+        <v>125598526</v>
       </c>
       <c r="B20" t="n">
-        <v>82779</v>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527573</v>
+        <v>527563</v>
       </c>
       <c r="R20" t="n">
-        <v>7059654</v>
+        <v>7059540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598526</v>
+        <v>125598562</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>82779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527563</v>
+        <v>527573</v>
       </c>
       <c r="R21" t="n">
-        <v>7059540</v>
+        <v>7059654</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
         <v>125598574</v>
       </c>
       <c r="B22" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125598575</v>
       </c>
       <c r="B23" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598561</v>
+        <v>125598579</v>
       </c>
       <c r="B25" t="n">
-        <v>82779</v>
+        <v>77916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527520</v>
+        <v>527524</v>
       </c>
       <c r="R25" t="n">
-        <v>7059331</v>
+        <v>7059550</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598579</v>
+        <v>125598522</v>
       </c>
       <c r="B26" t="n">
-        <v>77916</v>
+        <v>80070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527524</v>
+        <v>527884</v>
       </c>
       <c r="R26" t="n">
-        <v>7059550</v>
+        <v>7059787</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598450</v>
+        <v>125598561</v>
       </c>
       <c r="B27" t="n">
-        <v>75066</v>
+        <v>82779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527522</v>
+        <v>527520</v>
       </c>
       <c r="R27" t="n">
-        <v>7059339</v>
+        <v>7059331</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598522</v>
+        <v>125598450</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>75066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527884</v>
+        <v>527522</v>
       </c>
       <c r="R28" t="n">
-        <v>7059787</v>
+        <v>7059339</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,7 +3554,7 @@
         <v>125598456</v>
       </c>
       <c r="B30" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>125598482</v>
       </c>
       <c r="B31" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598468</v>
+        <v>125598457</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>96584</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
         <v>527542</v>
       </c>
       <c r="R32" t="n">
-        <v>7059620</v>
+        <v>7059349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598481</v>
+        <v>125598468</v>
       </c>
       <c r="B33" t="n">
-        <v>91220</v>
+        <v>79585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527880</v>
+        <v>527542</v>
       </c>
       <c r="R33" t="n">
-        <v>7059774</v>
+        <v>7059620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598521</v>
+        <v>125598481</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527890</v>
+        <v>527880</v>
       </c>
       <c r="R34" t="n">
-        <v>7059852</v>
+        <v>7059774</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598457</v>
+        <v>125598521</v>
       </c>
       <c r="B35" t="n">
-        <v>96577</v>
+        <v>80070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527542</v>
+        <v>527890</v>
       </c>
       <c r="R35" t="n">
-        <v>7059349</v>
+        <v>7059852</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598465</v>
+        <v>125598454</v>
       </c>
       <c r="B36" t="n">
-        <v>79585</v>
+        <v>96584</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528141</v>
+        <v>528167</v>
       </c>
       <c r="R36" t="n">
-        <v>7059905</v>
+        <v>7059940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598576</v>
+        <v>125598566</v>
       </c>
       <c r="B37" t="n">
-        <v>75058</v>
+        <v>91485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527583</v>
+        <v>527975</v>
       </c>
       <c r="R37" t="n">
-        <v>7059611</v>
+        <v>7059791</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598466</v>
+        <v>125598465</v>
       </c>
       <c r="B38" t="n">
         <v>79585</v>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527759</v>
+        <v>528141</v>
       </c>
       <c r="R38" t="n">
-        <v>7059678</v>
+        <v>7059905</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598512</v>
+        <v>125598576</v>
       </c>
       <c r="B39" t="n">
-        <v>80071</v>
+        <v>75058</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527496</v>
+        <v>527583</v>
       </c>
       <c r="R39" t="n">
-        <v>7059466</v>
+        <v>7059611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598475</v>
+        <v>125598466</v>
       </c>
       <c r="B40" t="n">
-        <v>79556</v>
+        <v>79585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528015</v>
+        <v>527759</v>
       </c>
       <c r="R40" t="n">
-        <v>7059826</v>
+        <v>7059678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598454</v>
+        <v>125598512</v>
       </c>
       <c r="B41" t="n">
-        <v>96577</v>
+        <v>80071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528167</v>
+        <v>527496</v>
       </c>
       <c r="R41" t="n">
-        <v>7059940</v>
+        <v>7059466</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,32 +4715,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598566</v>
+        <v>125598475</v>
       </c>
       <c r="B42" t="n">
-        <v>91478</v>
+        <v>79556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527975</v>
+        <v>528015</v>
       </c>
       <c r="R42" t="n">
-        <v>7059791</v>
+        <v>7059826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598455</v>
+        <v>125598509</v>
       </c>
       <c r="B51" t="n">
-        <v>96577</v>
+        <v>80071</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527827</v>
+        <v>528048</v>
       </c>
       <c r="R51" t="n">
-        <v>7059738</v>
+        <v>7059876</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598509</v>
+        <v>125598455</v>
       </c>
       <c r="B52" t="n">
-        <v>80071</v>
+        <v>96584</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528048</v>
+        <v>527827</v>
       </c>
       <c r="R52" t="n">
-        <v>7059876</v>
+        <v>7059738</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598449</v>
+        <v>125598543</v>
       </c>
       <c r="B54" t="n">
-        <v>75066</v>
+        <v>91387</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528035</v>
+        <v>527509</v>
       </c>
       <c r="R54" t="n">
-        <v>7059829</v>
+        <v>7059455</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5976,10 +5976,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598536</v>
+        <v>125598449</v>
       </c>
       <c r="B55" t="n">
-        <v>78725</v>
+        <v>75066</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527559</v>
+        <v>528035</v>
       </c>
       <c r="R55" t="n">
-        <v>7059578</v>
+        <v>7059829</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6073,32 +6073,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598543</v>
+        <v>125598536</v>
       </c>
       <c r="B56" t="n">
-        <v>91380</v>
+        <v>78725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527509</v>
+        <v>527559</v>
       </c>
       <c r="R56" t="n">
-        <v>7059455</v>
+        <v>7059578</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598511</v>
+        <v>125598458</v>
       </c>
       <c r="B57" t="n">
-        <v>80071</v>
+        <v>96584</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527884</v>
+        <v>527539</v>
       </c>
       <c r="R57" t="n">
-        <v>7059785</v>
+        <v>7059464</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598458</v>
+        <v>125598511</v>
       </c>
       <c r="B58" t="n">
-        <v>96577</v>
+        <v>80071</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527539</v>
+        <v>527884</v>
       </c>
       <c r="R58" t="n">
-        <v>7059464</v>
+        <v>7059785</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598556</v>
+        <v>125598525</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527522</v>
+        <v>527496</v>
       </c>
       <c r="R59" t="n">
-        <v>7059566</v>
+        <v>7059466</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,32 +6461,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598516</v>
+        <v>125598556</v>
       </c>
       <c r="B60" t="n">
-        <v>74877</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527519</v>
+        <v>527522</v>
       </c>
       <c r="R60" t="n">
-        <v>7059332</v>
+        <v>7059566</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598525</v>
+        <v>125598516</v>
       </c>
       <c r="B61" t="n">
-        <v>80070</v>
+        <v>74877</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527496</v>
+        <v>527519</v>
       </c>
       <c r="R61" t="n">
-        <v>7059466</v>
+        <v>7059332</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125598499</v>
+        <v>125598498</v>
       </c>
       <c r="B62" t="n">
         <v>57651</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527590</v>
+        <v>527595</v>
       </c>
       <c r="R62" t="n">
-        <v>7059608</v>
+        <v>7059511</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack &lt;5år</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125598498</v>
+        <v>125598499</v>
       </c>
       <c r="B63" t="n">
         <v>57651</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527595</v>
+        <v>527590</v>
       </c>
       <c r="R63" t="n">
-        <v>7059511</v>
+        <v>7059608</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack &lt;5år</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125598491</v>
+        <v>125598489</v>
       </c>
       <c r="B65" t="n">
         <v>57651</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527835</v>
+        <v>527850</v>
       </c>
       <c r="R65" t="n">
-        <v>7059763</v>
+        <v>7059804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125598489</v>
+        <v>125598491</v>
       </c>
       <c r="B66" t="n">
         <v>57651</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527850</v>
+        <v>527835</v>
       </c>
       <c r="R66" t="n">
-        <v>7059804</v>
+        <v>7059763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125598496</v>
+        <v>125598500</v>
       </c>
       <c r="B69" t="n">
         <v>57651</v>
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527610</v>
+        <v>527614</v>
       </c>
       <c r="R69" t="n">
-        <v>7059504</v>
+        <v>7059597</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125598500</v>
+        <v>125598496</v>
       </c>
       <c r="B70" t="n">
         <v>57651</v>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527614</v>
+        <v>527610</v>
       </c>
       <c r="R70" t="n">
-        <v>7059597</v>
+        <v>7059504</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598454</v>
+        <v>125598475</v>
       </c>
       <c r="B36" t="n">
-        <v>96584</v>
+        <v>79556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528167</v>
+        <v>528015</v>
       </c>
       <c r="R36" t="n">
-        <v>7059940</v>
+        <v>7059826</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598566</v>
+        <v>125598454</v>
       </c>
       <c r="B37" t="n">
-        <v>91485</v>
+        <v>96584</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527975</v>
+        <v>528167</v>
       </c>
       <c r="R37" t="n">
-        <v>7059791</v>
+        <v>7059940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598465</v>
+        <v>125598566</v>
       </c>
       <c r="B38" t="n">
-        <v>79585</v>
+        <v>91485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528141</v>
+        <v>527975</v>
       </c>
       <c r="R38" t="n">
-        <v>7059905</v>
+        <v>7059791</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598576</v>
+        <v>125598465</v>
       </c>
       <c r="B39" t="n">
-        <v>75058</v>
+        <v>79585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527583</v>
+        <v>528141</v>
       </c>
       <c r="R39" t="n">
-        <v>7059611</v>
+        <v>7059905</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598466</v>
+        <v>125598576</v>
       </c>
       <c r="B40" t="n">
-        <v>79585</v>
+        <v>75058</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527759</v>
+        <v>527583</v>
       </c>
       <c r="R40" t="n">
-        <v>7059678</v>
+        <v>7059611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598512</v>
+        <v>125598466</v>
       </c>
       <c r="B41" t="n">
-        <v>80071</v>
+        <v>79585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527496</v>
+        <v>527759</v>
       </c>
       <c r="R41" t="n">
-        <v>7059466</v>
+        <v>7059678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598475</v>
+        <v>125598512</v>
       </c>
       <c r="B42" t="n">
-        <v>79556</v>
+        <v>80071</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528015</v>
+        <v>527496</v>
       </c>
       <c r="R42" t="n">
-        <v>7059826</v>
+        <v>7059466</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598579</v>
+        <v>125598561</v>
       </c>
       <c r="B25" t="n">
-        <v>77916</v>
+        <v>82779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527524</v>
+        <v>527520</v>
       </c>
       <c r="R25" t="n">
-        <v>7059550</v>
+        <v>7059331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598522</v>
+        <v>125598450</v>
       </c>
       <c r="B26" t="n">
-        <v>80070</v>
+        <v>75066</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527884</v>
+        <v>527522</v>
       </c>
       <c r="R26" t="n">
-        <v>7059787</v>
+        <v>7059339</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598561</v>
+        <v>125598579</v>
       </c>
       <c r="B27" t="n">
-        <v>82779</v>
+        <v>77916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527520</v>
+        <v>527524</v>
       </c>
       <c r="R27" t="n">
-        <v>7059331</v>
+        <v>7059550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598450</v>
+        <v>125598522</v>
       </c>
       <c r="B28" t="n">
-        <v>75066</v>
+        <v>80070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527522</v>
+        <v>527884</v>
       </c>
       <c r="R28" t="n">
-        <v>7059339</v>
+        <v>7059787</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598476</v>
+        <v>125598535</v>
       </c>
       <c r="B43" t="n">
-        <v>79556</v>
+        <v>78725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527488</v>
+        <v>527536</v>
       </c>
       <c r="R43" t="n">
-        <v>7059420</v>
+        <v>7059461</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598535</v>
+        <v>125598554</v>
       </c>
       <c r="B44" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527536</v>
+        <v>527561</v>
       </c>
       <c r="R44" t="n">
-        <v>7059461</v>
+        <v>7059318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598554</v>
+        <v>125598467</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527561</v>
+        <v>527570</v>
       </c>
       <c r="R45" t="n">
-        <v>7059318</v>
+        <v>7059603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598467</v>
+        <v>125598528</v>
       </c>
       <c r="B46" t="n">
-        <v>79585</v>
+        <v>80942</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527570</v>
+        <v>527479</v>
       </c>
       <c r="R46" t="n">
-        <v>7059603</v>
+        <v>7059420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598528</v>
+        <v>125598452</v>
       </c>
       <c r="B47" t="n">
-        <v>80942</v>
+        <v>75066</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527479</v>
+        <v>527573</v>
       </c>
       <c r="R47" t="n">
-        <v>7059420</v>
+        <v>7059652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598452</v>
+        <v>125598476</v>
       </c>
       <c r="B48" t="n">
-        <v>75066</v>
+        <v>79556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527573</v>
+        <v>527488</v>
       </c>
       <c r="R48" t="n">
-        <v>7059652</v>
+        <v>7059420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>125584011</v>
       </c>
       <c r="B7" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>125584025</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125583991</v>
       </c>
       <c r="B9" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>125598555</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125598557</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>125598519</v>
       </c>
       <c r="B12" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125598553</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>125598537</v>
       </c>
       <c r="B15" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>125598459</v>
       </c>
       <c r="B16" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>125598460</v>
       </c>
       <c r="B17" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>125598545</v>
       </c>
       <c r="B18" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125598510</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>125598526</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>125598562</v>
       </c>
       <c r="B21" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>125598574</v>
       </c>
       <c r="B22" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125598575</v>
       </c>
       <c r="B23" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>125598515</v>
       </c>
       <c r="B24" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598561</v>
+        <v>125598450</v>
       </c>
       <c r="B25" t="n">
-        <v>82779</v>
+        <v>75067</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527520</v>
+        <v>527522</v>
       </c>
       <c r="R25" t="n">
-        <v>7059331</v>
+        <v>7059339</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598450</v>
+        <v>125598522</v>
       </c>
       <c r="B26" t="n">
-        <v>75066</v>
+        <v>80071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527522</v>
+        <v>527884</v>
       </c>
       <c r="R26" t="n">
-        <v>7059339</v>
+        <v>7059787</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598579</v>
+        <v>125598561</v>
       </c>
       <c r="B27" t="n">
-        <v>77916</v>
+        <v>82780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527524</v>
+        <v>527520</v>
       </c>
       <c r="R27" t="n">
-        <v>7059550</v>
+        <v>7059331</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598522</v>
+        <v>125598579</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>77917</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527884</v>
+        <v>527524</v>
       </c>
       <c r="R28" t="n">
-        <v>7059787</v>
+        <v>7059550</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598448</v>
+        <v>125598456</v>
       </c>
       <c r="B29" t="n">
-        <v>75066</v>
+        <v>96587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528190</v>
+        <v>527574</v>
       </c>
       <c r="R29" t="n">
-        <v>7059902</v>
+        <v>7059456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598456</v>
+        <v>125598448</v>
       </c>
       <c r="B30" t="n">
-        <v>96584</v>
+        <v>75067</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527574</v>
+        <v>528190</v>
       </c>
       <c r="R30" t="n">
-        <v>7059456</v>
+        <v>7059902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598482</v>
+        <v>125598468</v>
       </c>
       <c r="B31" t="n">
-        <v>91227</v>
+        <v>79586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527578</v>
+        <v>527542</v>
       </c>
       <c r="R31" t="n">
-        <v>7059506</v>
+        <v>7059620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598457</v>
+        <v>125598482</v>
       </c>
       <c r="B32" t="n">
-        <v>96584</v>
+        <v>91228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527542</v>
+        <v>527578</v>
       </c>
       <c r="R32" t="n">
-        <v>7059349</v>
+        <v>7059506</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598468</v>
+        <v>125598457</v>
       </c>
       <c r="B33" t="n">
-        <v>79585</v>
+        <v>96587</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
         <v>527542</v>
       </c>
       <c r="R33" t="n">
-        <v>7059620</v>
+        <v>7059349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3942,7 @@
         <v>125598481</v>
       </c>
       <c r="B34" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>125598521</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598475</v>
+        <v>125598465</v>
       </c>
       <c r="B36" t="n">
-        <v>79556</v>
+        <v>79586</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528015</v>
+        <v>528141</v>
       </c>
       <c r="R36" t="n">
-        <v>7059826</v>
+        <v>7059905</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598454</v>
+        <v>125598466</v>
       </c>
       <c r="B37" t="n">
-        <v>96584</v>
+        <v>79586</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528167</v>
+        <v>527759</v>
       </c>
       <c r="R37" t="n">
-        <v>7059940</v>
+        <v>7059678</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598566</v>
+        <v>125598512</v>
       </c>
       <c r="B38" t="n">
-        <v>91485</v>
+        <v>80072</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527975</v>
+        <v>527496</v>
       </c>
       <c r="R38" t="n">
-        <v>7059791</v>
+        <v>7059466</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598465</v>
+        <v>125598454</v>
       </c>
       <c r="B39" t="n">
-        <v>79585</v>
+        <v>96587</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528141</v>
+        <v>528167</v>
       </c>
       <c r="R39" t="n">
-        <v>7059905</v>
+        <v>7059940</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,32 +4521,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598576</v>
+        <v>125598566</v>
       </c>
       <c r="B40" t="n">
-        <v>75058</v>
+        <v>91489</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527583</v>
+        <v>527975</v>
       </c>
       <c r="R40" t="n">
-        <v>7059611</v>
+        <v>7059791</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598466</v>
+        <v>125598576</v>
       </c>
       <c r="B41" t="n">
-        <v>79585</v>
+        <v>75059</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527759</v>
+        <v>527583</v>
       </c>
       <c r="R41" t="n">
-        <v>7059678</v>
+        <v>7059611</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598512</v>
+        <v>125598475</v>
       </c>
       <c r="B42" t="n">
-        <v>80071</v>
+        <v>79557</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527496</v>
+        <v>528015</v>
       </c>
       <c r="R42" t="n">
-        <v>7059466</v>
+        <v>7059826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4815,7 +4815,7 @@
         <v>125598535</v>
       </c>
       <c r="B43" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>125598554</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>125598467</v>
       </c>
       <c r="B45" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598528</v>
+        <v>125598452</v>
       </c>
       <c r="B46" t="n">
-        <v>80942</v>
+        <v>75067</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527479</v>
+        <v>527573</v>
       </c>
       <c r="R46" t="n">
-        <v>7059420</v>
+        <v>7059652</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598452</v>
+        <v>125598528</v>
       </c>
       <c r="B47" t="n">
-        <v>75066</v>
+        <v>80943</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527573</v>
+        <v>527479</v>
       </c>
       <c r="R47" t="n">
-        <v>7059652</v>
+        <v>7059420</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5300,7 +5300,7 @@
         <v>125598476</v>
       </c>
       <c r="B48" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>125598534</v>
       </c>
       <c r="B49" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B50" t="n">
-        <v>78726</v>
+        <v>80072</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R50" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598509</v>
+        <v>125598455</v>
       </c>
       <c r="B51" t="n">
-        <v>80071</v>
+        <v>96587</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528048</v>
+        <v>527827</v>
       </c>
       <c r="R51" t="n">
-        <v>7059876</v>
+        <v>7059738</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598455</v>
+        <v>125598520</v>
       </c>
       <c r="B52" t="n">
-        <v>96584</v>
+        <v>78727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527827</v>
+        <v>527925</v>
       </c>
       <c r="R52" t="n">
-        <v>7059738</v>
+        <v>7059867</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5785,7 +5785,7 @@
         <v>125598451</v>
       </c>
       <c r="B53" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598543</v>
+        <v>125598449</v>
       </c>
       <c r="B54" t="n">
-        <v>91387</v>
+        <v>75067</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527509</v>
+        <v>528035</v>
       </c>
       <c r="R54" t="n">
-        <v>7059455</v>
+        <v>7059829</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5976,10 +5976,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598449</v>
+        <v>125598536</v>
       </c>
       <c r="B55" t="n">
-        <v>75066</v>
+        <v>78726</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528035</v>
+        <v>527559</v>
       </c>
       <c r="R55" t="n">
-        <v>7059829</v>
+        <v>7059578</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6073,32 +6073,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598536</v>
+        <v>125598543</v>
       </c>
       <c r="B56" t="n">
-        <v>78725</v>
+        <v>91389</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527559</v>
+        <v>527509</v>
       </c>
       <c r="R56" t="n">
-        <v>7059578</v>
+        <v>7059455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598458</v>
+        <v>125598511</v>
       </c>
       <c r="B57" t="n">
-        <v>96584</v>
+        <v>80072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527539</v>
+        <v>527884</v>
       </c>
       <c r="R57" t="n">
-        <v>7059464</v>
+        <v>7059785</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598511</v>
+        <v>125598458</v>
       </c>
       <c r="B58" t="n">
-        <v>80071</v>
+        <v>96587</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527884</v>
+        <v>527539</v>
       </c>
       <c r="R58" t="n">
-        <v>7059785</v>
+        <v>7059464</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598525</v>
+        <v>125598556</v>
       </c>
       <c r="B59" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527496</v>
+        <v>527522</v>
       </c>
       <c r="R59" t="n">
-        <v>7059466</v>
+        <v>7059566</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,32 +6461,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598556</v>
+        <v>125598516</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>74878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527522</v>
+        <v>527519</v>
       </c>
       <c r="R60" t="n">
-        <v>7059566</v>
+        <v>7059332</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598516</v>
+        <v>125598525</v>
       </c>
       <c r="B61" t="n">
-        <v>74877</v>
+        <v>80071</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527519</v>
+        <v>527496</v>
       </c>
       <c r="R61" t="n">
-        <v>7059332</v>
+        <v>7059466</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125598498</v>
+        <v>125598499</v>
       </c>
       <c r="B62" t="n">
         <v>57651</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527595</v>
+        <v>527590</v>
       </c>
       <c r="R62" t="n">
-        <v>7059511</v>
+        <v>7059608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack &lt;5år</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125598499</v>
+        <v>125598498</v>
       </c>
       <c r="B63" t="n">
         <v>57651</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527590</v>
+        <v>527595</v>
       </c>
       <c r="R63" t="n">
-        <v>7059608</v>
+        <v>7059511</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack &lt;5år</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598526</v>
+        <v>125598562</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>82780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527563</v>
+        <v>527573</v>
       </c>
       <c r="R20" t="n">
-        <v>7059540</v>
+        <v>7059654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598562</v>
+        <v>125598526</v>
       </c>
       <c r="B21" t="n">
-        <v>82780</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527573</v>
+        <v>527563</v>
       </c>
       <c r="R21" t="n">
-        <v>7059654</v>
+        <v>7059540</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598468</v>
+        <v>125598482</v>
       </c>
       <c r="B31" t="n">
-        <v>79586</v>
+        <v>91228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527542</v>
+        <v>527578</v>
       </c>
       <c r="R31" t="n">
-        <v>7059620</v>
+        <v>7059506</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598482</v>
+        <v>125598457</v>
       </c>
       <c r="B32" t="n">
-        <v>91228</v>
+        <v>96587</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527578</v>
+        <v>527542</v>
       </c>
       <c r="R32" t="n">
-        <v>7059506</v>
+        <v>7059349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598457</v>
+        <v>125598481</v>
       </c>
       <c r="B33" t="n">
-        <v>96587</v>
+        <v>91228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527542</v>
+        <v>527880</v>
       </c>
       <c r="R33" t="n">
-        <v>7059349</v>
+        <v>7059774</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598481</v>
+        <v>125598521</v>
       </c>
       <c r="B34" t="n">
-        <v>91228</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527880</v>
+        <v>527890</v>
       </c>
       <c r="R34" t="n">
-        <v>7059774</v>
+        <v>7059852</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598521</v>
+        <v>125598468</v>
       </c>
       <c r="B35" t="n">
-        <v>80071</v>
+        <v>79586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527890</v>
+        <v>527542</v>
       </c>
       <c r="R35" t="n">
-        <v>7059852</v>
+        <v>7059620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598535</v>
+        <v>125598476</v>
       </c>
       <c r="B43" t="n">
-        <v>78726</v>
+        <v>79557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527536</v>
+        <v>527488</v>
       </c>
       <c r="R43" t="n">
-        <v>7059461</v>
+        <v>7059420</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598554</v>
+        <v>125598535</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78726</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527561</v>
+        <v>527536</v>
       </c>
       <c r="R44" t="n">
-        <v>7059318</v>
+        <v>7059461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598467</v>
+        <v>125598554</v>
       </c>
       <c r="B45" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527570</v>
+        <v>527561</v>
       </c>
       <c r="R45" t="n">
-        <v>7059603</v>
+        <v>7059318</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598452</v>
+        <v>125598467</v>
       </c>
       <c r="B46" t="n">
-        <v>75067</v>
+        <v>79586</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527573</v>
+        <v>527570</v>
       </c>
       <c r="R46" t="n">
-        <v>7059652</v>
+        <v>7059603</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598528</v>
+        <v>125598452</v>
       </c>
       <c r="B47" t="n">
-        <v>80943</v>
+        <v>75067</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527479</v>
+        <v>527573</v>
       </c>
       <c r="R47" t="n">
-        <v>7059420</v>
+        <v>7059652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598476</v>
+        <v>125598528</v>
       </c>
       <c r="B48" t="n">
-        <v>79557</v>
+        <v>80943</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527488</v>
+        <v>527479</v>
       </c>
       <c r="R48" t="n">
         <v>7059420</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>125584011</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>125584025</v>
       </c>
       <c r="B8" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125583991</v>
       </c>
       <c r="B9" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>125598555</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125598557</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>125598519</v>
       </c>
       <c r="B12" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125598553</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598537</v>
+        <v>125598459</v>
       </c>
       <c r="B15" t="n">
-        <v>91389</v>
+        <v>96591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528146</v>
+        <v>527589</v>
       </c>
       <c r="R15" t="n">
-        <v>7059953</v>
+        <v>7059511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598459</v>
+        <v>125598537</v>
       </c>
       <c r="B16" t="n">
-        <v>96587</v>
+        <v>91393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527589</v>
+        <v>528146</v>
       </c>
       <c r="R16" t="n">
-        <v>7059511</v>
+        <v>7059953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598460</v>
+        <v>125598545</v>
       </c>
       <c r="B17" t="n">
-        <v>96587</v>
+        <v>91393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527527</v>
+        <v>527569</v>
       </c>
       <c r="R17" t="n">
-        <v>7059584</v>
+        <v>7059499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598545</v>
+        <v>125598460</v>
       </c>
       <c r="B18" t="n">
-        <v>91389</v>
+        <v>96591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527569</v>
+        <v>527527</v>
       </c>
       <c r="R18" t="n">
-        <v>7059499</v>
+        <v>7059584</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
         <v>125598510</v>
       </c>
       <c r="B19" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>125598562</v>
       </c>
       <c r="B20" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>125598526</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>125598574</v>
       </c>
       <c r="B22" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125598575</v>
       </c>
       <c r="B23" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>125598515</v>
       </c>
       <c r="B24" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598450</v>
+        <v>125598561</v>
       </c>
       <c r="B25" t="n">
-        <v>75067</v>
+        <v>82784</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527522</v>
+        <v>527520</v>
       </c>
       <c r="R25" t="n">
-        <v>7059339</v>
+        <v>7059331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598522</v>
+        <v>125598579</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>77921</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527884</v>
+        <v>527524</v>
       </c>
       <c r="R26" t="n">
-        <v>7059787</v>
+        <v>7059550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598561</v>
+        <v>125598522</v>
       </c>
       <c r="B27" t="n">
-        <v>82780</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527520</v>
+        <v>527884</v>
       </c>
       <c r="R27" t="n">
-        <v>7059331</v>
+        <v>7059787</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598579</v>
+        <v>125598450</v>
       </c>
       <c r="B28" t="n">
-        <v>77917</v>
+        <v>75067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527524</v>
+        <v>527522</v>
       </c>
       <c r="R28" t="n">
-        <v>7059550</v>
+        <v>7059339</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>125598456</v>
       </c>
       <c r="B29" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598482</v>
+        <v>125598521</v>
       </c>
       <c r="B31" t="n">
-        <v>91228</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527578</v>
+        <v>527890</v>
       </c>
       <c r="R31" t="n">
-        <v>7059506</v>
+        <v>7059852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598457</v>
+        <v>125598468</v>
       </c>
       <c r="B32" t="n">
-        <v>96587</v>
+        <v>79590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
         <v>527542</v>
       </c>
       <c r="R32" t="n">
-        <v>7059349</v>
+        <v>7059620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598481</v>
+        <v>125598482</v>
       </c>
       <c r="B33" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527880</v>
+        <v>527578</v>
       </c>
       <c r="R33" t="n">
-        <v>7059774</v>
+        <v>7059506</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598521</v>
+        <v>125598457</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>96591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527890</v>
+        <v>527542</v>
       </c>
       <c r="R34" t="n">
-        <v>7059852</v>
+        <v>7059349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598468</v>
+        <v>125598481</v>
       </c>
       <c r="B35" t="n">
-        <v>79586</v>
+        <v>91232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527542</v>
+        <v>527880</v>
       </c>
       <c r="R35" t="n">
-        <v>7059620</v>
+        <v>7059774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598465</v>
+        <v>125598512</v>
       </c>
       <c r="B36" t="n">
-        <v>79586</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528141</v>
+        <v>527496</v>
       </c>
       <c r="R36" t="n">
-        <v>7059905</v>
+        <v>7059466</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598466</v>
+        <v>125598475</v>
       </c>
       <c r="B37" t="n">
-        <v>79586</v>
+        <v>79561</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527759</v>
+        <v>528015</v>
       </c>
       <c r="R37" t="n">
-        <v>7059678</v>
+        <v>7059826</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,10 +4327,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598512</v>
+        <v>125598454</v>
       </c>
       <c r="B38" t="n">
-        <v>80072</v>
+        <v>96591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,21 +4338,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527496</v>
+        <v>528167</v>
       </c>
       <c r="R38" t="n">
-        <v>7059466</v>
+        <v>7059940</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,32 +4424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598454</v>
+        <v>125598566</v>
       </c>
       <c r="B39" t="n">
-        <v>96587</v>
+        <v>91493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528167</v>
+        <v>527975</v>
       </c>
       <c r="R39" t="n">
-        <v>7059940</v>
+        <v>7059791</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,32 +4521,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598566</v>
+        <v>125598576</v>
       </c>
       <c r="B40" t="n">
-        <v>91489</v>
+        <v>75059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527975</v>
+        <v>527583</v>
       </c>
       <c r="R40" t="n">
-        <v>7059791</v>
+        <v>7059611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598576</v>
+        <v>125598465</v>
       </c>
       <c r="B41" t="n">
-        <v>75059</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527583</v>
+        <v>528141</v>
       </c>
       <c r="R41" t="n">
-        <v>7059611</v>
+        <v>7059905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598475</v>
+        <v>125598466</v>
       </c>
       <c r="B42" t="n">
-        <v>79557</v>
+        <v>79590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528015</v>
+        <v>527759</v>
       </c>
       <c r="R42" t="n">
-        <v>7059826</v>
+        <v>7059678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598476</v>
+        <v>125598528</v>
       </c>
       <c r="B43" t="n">
-        <v>79557</v>
+        <v>80947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527488</v>
+        <v>527479</v>
       </c>
       <c r="R43" t="n">
         <v>7059420</v>
@@ -4912,7 +4912,7 @@
         <v>125598535</v>
       </c>
       <c r="B44" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598554</v>
+        <v>125598452</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527561</v>
+        <v>527573</v>
       </c>
       <c r="R45" t="n">
-        <v>7059318</v>
+        <v>7059652</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5106,7 +5106,7 @@
         <v>125598467</v>
       </c>
       <c r="B46" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598452</v>
+        <v>125598554</v>
       </c>
       <c r="B47" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527573</v>
+        <v>527561</v>
       </c>
       <c r="R47" t="n">
-        <v>7059652</v>
+        <v>7059318</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598528</v>
+        <v>125598476</v>
       </c>
       <c r="B48" t="n">
-        <v>80943</v>
+        <v>79561</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527479</v>
+        <v>527488</v>
       </c>
       <c r="R48" t="n">
         <v>7059420</v>
@@ -5397,7 +5397,7 @@
         <v>125598534</v>
       </c>
       <c r="B49" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>125598509</v>
       </c>
       <c r="B50" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>125598455</v>
       </c>
       <c r="B51" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>125598520</v>
       </c>
       <c r="B52" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125598451</v>
+        <v>125598536</v>
       </c>
       <c r="B53" t="n">
-        <v>75067</v>
+        <v>78730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5793,21 +5793,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527552</v>
+        <v>527559</v>
       </c>
       <c r="R53" t="n">
-        <v>7059543</v>
+        <v>7059578</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598449</v>
+        <v>125598451</v>
       </c>
       <c r="B54" t="n">
         <v>75067</v>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528035</v>
+        <v>527552</v>
       </c>
       <c r="R54" t="n">
-        <v>7059829</v>
+        <v>7059543</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5976,10 +5976,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598536</v>
+        <v>125598449</v>
       </c>
       <c r="B55" t="n">
-        <v>78726</v>
+        <v>75067</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527559</v>
+        <v>528035</v>
       </c>
       <c r="R55" t="n">
-        <v>7059578</v>
+        <v>7059829</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6076,7 +6076,7 @@
         <v>125598543</v>
       </c>
       <c r="B56" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598511</v>
+        <v>125598458</v>
       </c>
       <c r="B57" t="n">
-        <v>80072</v>
+        <v>96591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527884</v>
+        <v>527539</v>
       </c>
       <c r="R57" t="n">
-        <v>7059785</v>
+        <v>7059464</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598458</v>
+        <v>125598511</v>
       </c>
       <c r="B58" t="n">
-        <v>96587</v>
+        <v>80076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527539</v>
+        <v>527884</v>
       </c>
       <c r="R58" t="n">
-        <v>7059464</v>
+        <v>7059785</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598556</v>
+        <v>125598525</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527522</v>
+        <v>527496</v>
       </c>
       <c r="R59" t="n">
-        <v>7059566</v>
+        <v>7059466</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,32 +6461,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598516</v>
+        <v>125598556</v>
       </c>
       <c r="B60" t="n">
-        <v>74878</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527519</v>
+        <v>527522</v>
       </c>
       <c r="R60" t="n">
-        <v>7059332</v>
+        <v>7059566</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598525</v>
+        <v>125598516</v>
       </c>
       <c r="B61" t="n">
-        <v>80071</v>
+        <v>74878</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527496</v>
+        <v>527519</v>
       </c>
       <c r="R61" t="n">
-        <v>7059466</v>
+        <v>7059332</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125598499</v>
+        <v>125598498</v>
       </c>
       <c r="B62" t="n">
         <v>57651</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527590</v>
+        <v>527595</v>
       </c>
       <c r="R62" t="n">
-        <v>7059608</v>
+        <v>7059511</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack &lt;5år</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125598498</v>
+        <v>125598499</v>
       </c>
       <c r="B63" t="n">
         <v>57651</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527595</v>
+        <v>527590</v>
       </c>
       <c r="R63" t="n">
-        <v>7059511</v>
+        <v>7059608</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack &lt;5år</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1999,32 +1999,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598461</v>
+        <v>125598537</v>
       </c>
       <c r="B14" t="n">
-        <v>96591</v>
+        <v>91393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527527</v>
+        <v>528146</v>
       </c>
       <c r="R14" t="n">
-        <v>7059604</v>
+        <v>7059953</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598459</v>
+        <v>125598461</v>
       </c>
       <c r="B15" t="n">
         <v>96591</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527589</v>
+        <v>527527</v>
       </c>
       <c r="R15" t="n">
-        <v>7059511</v>
+        <v>7059604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598537</v>
+        <v>125598459</v>
       </c>
       <c r="B16" t="n">
-        <v>91393</v>
+        <v>96591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528146</v>
+        <v>527589</v>
       </c>
       <c r="R16" t="n">
-        <v>7059953</v>
+        <v>7059511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598562</v>
+        <v>125598526</v>
       </c>
       <c r="B20" t="n">
-        <v>82784</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527573</v>
+        <v>527563</v>
       </c>
       <c r="R20" t="n">
-        <v>7059654</v>
+        <v>7059540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598526</v>
+        <v>125598562</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>82784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527563</v>
+        <v>527573</v>
       </c>
       <c r="R21" t="n">
-        <v>7059540</v>
+        <v>7059654</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598512</v>
+        <v>125598475</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>79561</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527496</v>
+        <v>528015</v>
       </c>
       <c r="R36" t="n">
-        <v>7059466</v>
+        <v>7059826</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598475</v>
+        <v>125598454</v>
       </c>
       <c r="B37" t="n">
-        <v>79561</v>
+        <v>96591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528015</v>
+        <v>528167</v>
       </c>
       <c r="R37" t="n">
-        <v>7059826</v>
+        <v>7059940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598454</v>
+        <v>125598566</v>
       </c>
       <c r="B38" t="n">
-        <v>96591</v>
+        <v>91493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528167</v>
+        <v>527975</v>
       </c>
       <c r="R38" t="n">
-        <v>7059940</v>
+        <v>7059791</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,32 +4424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598566</v>
+        <v>125598576</v>
       </c>
       <c r="B39" t="n">
-        <v>91493</v>
+        <v>75059</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527975</v>
+        <v>527583</v>
       </c>
       <c r="R39" t="n">
-        <v>7059791</v>
+        <v>7059611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598576</v>
+        <v>125598512</v>
       </c>
       <c r="B40" t="n">
-        <v>75059</v>
+        <v>80076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527583</v>
+        <v>527496</v>
       </c>
       <c r="R40" t="n">
-        <v>7059611</v>
+        <v>7059466</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598509</v>
+        <v>125598455</v>
       </c>
       <c r="B50" t="n">
-        <v>80076</v>
+        <v>96591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528048</v>
+        <v>527827</v>
       </c>
       <c r="R50" t="n">
-        <v>7059876</v>
+        <v>7059738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598455</v>
+        <v>125598520</v>
       </c>
       <c r="B51" t="n">
-        <v>96591</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527827</v>
+        <v>527925</v>
       </c>
       <c r="R51" t="n">
-        <v>7059738</v>
+        <v>7059867</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R52" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1999,32 +1999,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125598537</v>
+        <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>91393</v>
+        <v>96592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528146</v>
+        <v>527527</v>
       </c>
       <c r="R14" t="n">
-        <v>7059953</v>
+        <v>7059604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598461</v>
+        <v>125598459</v>
       </c>
       <c r="B15" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527527</v>
+        <v>527589</v>
       </c>
       <c r="R15" t="n">
-        <v>7059604</v>
+        <v>7059511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598459</v>
+        <v>125598537</v>
       </c>
       <c r="B16" t="n">
-        <v>96591</v>
+        <v>91393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527589</v>
+        <v>528146</v>
       </c>
       <c r="R16" t="n">
-        <v>7059511</v>
+        <v>7059953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598545</v>
+        <v>125598460</v>
       </c>
       <c r="B17" t="n">
-        <v>91393</v>
+        <v>96592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527569</v>
+        <v>527527</v>
       </c>
       <c r="R17" t="n">
-        <v>7059499</v>
+        <v>7059584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598460</v>
+        <v>125598545</v>
       </c>
       <c r="B18" t="n">
-        <v>96591</v>
+        <v>91393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527527</v>
+        <v>527569</v>
       </c>
       <c r="R18" t="n">
-        <v>7059584</v>
+        <v>7059499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598526</v>
+        <v>125598562</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>82784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527563</v>
+        <v>527573</v>
       </c>
       <c r="R20" t="n">
-        <v>7059540</v>
+        <v>7059654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598562</v>
+        <v>125598526</v>
       </c>
       <c r="B21" t="n">
-        <v>82784</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527573</v>
+        <v>527563</v>
       </c>
       <c r="R21" t="n">
-        <v>7059654</v>
+        <v>7059540</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598561</v>
+        <v>125598450</v>
       </c>
       <c r="B25" t="n">
-        <v>82784</v>
+        <v>75067</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527520</v>
+        <v>527522</v>
       </c>
       <c r="R25" t="n">
-        <v>7059331</v>
+        <v>7059339</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598450</v>
+        <v>125598561</v>
       </c>
       <c r="B28" t="n">
-        <v>75067</v>
+        <v>82784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527522</v>
+        <v>527520</v>
       </c>
       <c r="R28" t="n">
-        <v>7059339</v>
+        <v>7059331</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>125598456</v>
       </c>
       <c r="B29" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598521</v>
+        <v>125598457</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>96592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527890</v>
+        <v>527542</v>
       </c>
       <c r="R31" t="n">
-        <v>7059852</v>
+        <v>7059349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598468</v>
+        <v>125598482</v>
       </c>
       <c r="B32" t="n">
-        <v>79590</v>
+        <v>91232</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527542</v>
+        <v>527578</v>
       </c>
       <c r="R32" t="n">
-        <v>7059620</v>
+        <v>7059506</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598482</v>
+        <v>125598481</v>
       </c>
       <c r="B33" t="n">
         <v>91232</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527578</v>
+        <v>527880</v>
       </c>
       <c r="R33" t="n">
-        <v>7059506</v>
+        <v>7059774</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598457</v>
+        <v>125598468</v>
       </c>
       <c r="B34" t="n">
-        <v>96591</v>
+        <v>79590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3977,7 +3977,7 @@
         <v>527542</v>
       </c>
       <c r="R34" t="n">
-        <v>7059349</v>
+        <v>7059620</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598481</v>
+        <v>125598521</v>
       </c>
       <c r="B35" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527880</v>
+        <v>527890</v>
       </c>
       <c r="R35" t="n">
-        <v>7059774</v>
+        <v>7059852</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598475</v>
+        <v>125598465</v>
       </c>
       <c r="B36" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528015</v>
+        <v>528141</v>
       </c>
       <c r="R36" t="n">
-        <v>7059826</v>
+        <v>7059905</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598454</v>
+        <v>125598466</v>
       </c>
       <c r="B37" t="n">
-        <v>96591</v>
+        <v>79590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4241,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528167</v>
+        <v>527759</v>
       </c>
       <c r="R37" t="n">
-        <v>7059940</v>
+        <v>7059678</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598566</v>
+        <v>125598454</v>
       </c>
       <c r="B38" t="n">
-        <v>91493</v>
+        <v>96592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527975</v>
+        <v>528167</v>
       </c>
       <c r="R38" t="n">
-        <v>7059791</v>
+        <v>7059940</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,32 +4424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598576</v>
+        <v>125598566</v>
       </c>
       <c r="B39" t="n">
-        <v>75059</v>
+        <v>91493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527583</v>
+        <v>527975</v>
       </c>
       <c r="R39" t="n">
-        <v>7059611</v>
+        <v>7059791</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598512</v>
+        <v>125598576</v>
       </c>
       <c r="B40" t="n">
-        <v>80076</v>
+        <v>75059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527496</v>
+        <v>527583</v>
       </c>
       <c r="R40" t="n">
-        <v>7059466</v>
+        <v>7059611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598465</v>
+        <v>125598512</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528141</v>
+        <v>527496</v>
       </c>
       <c r="R41" t="n">
-        <v>7059905</v>
+        <v>7059466</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598466</v>
+        <v>125598475</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527759</v>
+        <v>528015</v>
       </c>
       <c r="R42" t="n">
-        <v>7059678</v>
+        <v>7059826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598528</v>
+        <v>125598476</v>
       </c>
       <c r="B43" t="n">
-        <v>80947</v>
+        <v>79561</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527479</v>
+        <v>527488</v>
       </c>
       <c r="R43" t="n">
         <v>7059420</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598535</v>
+        <v>125598528</v>
       </c>
       <c r="B44" t="n">
-        <v>78730</v>
+        <v>80947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527536</v>
+        <v>527479</v>
       </c>
       <c r="R44" t="n">
-        <v>7059461</v>
+        <v>7059420</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598452</v>
+        <v>125598535</v>
       </c>
       <c r="B45" t="n">
-        <v>75067</v>
+        <v>78730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527573</v>
+        <v>527536</v>
       </c>
       <c r="R45" t="n">
-        <v>7059652</v>
+        <v>7059461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598467</v>
+        <v>125598554</v>
       </c>
       <c r="B46" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527570</v>
+        <v>527561</v>
       </c>
       <c r="R46" t="n">
-        <v>7059603</v>
+        <v>7059318</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598554</v>
+        <v>125598467</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527561</v>
+        <v>527570</v>
       </c>
       <c r="R47" t="n">
-        <v>7059318</v>
+        <v>7059603</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598476</v>
+        <v>125598452</v>
       </c>
       <c r="B48" t="n">
-        <v>79561</v>
+        <v>75067</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527488</v>
+        <v>527573</v>
       </c>
       <c r="R48" t="n">
-        <v>7059420</v>
+        <v>7059652</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
         <v>125598455</v>
       </c>
       <c r="B50" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R51" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598509</v>
+        <v>125598520</v>
       </c>
       <c r="B52" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528048</v>
+        <v>527925</v>
       </c>
       <c r="R52" t="n">
-        <v>7059876</v>
+        <v>7059867</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5782,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125598536</v>
+        <v>125598543</v>
       </c>
       <c r="B53" t="n">
-        <v>78730</v>
+        <v>91393</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527559</v>
+        <v>527509</v>
       </c>
       <c r="R53" t="n">
-        <v>7059578</v>
+        <v>7059455</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6073,32 +6073,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598543</v>
+        <v>125598536</v>
       </c>
       <c r="B56" t="n">
-        <v>91393</v>
+        <v>78730</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527509</v>
+        <v>527559</v>
       </c>
       <c r="R56" t="n">
-        <v>7059455</v>
+        <v>7059578</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6173,7 +6173,7 @@
         <v>125598458</v>
       </c>
       <c r="B57" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125598525</v>
+        <v>125598556</v>
       </c>
       <c r="B59" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527496</v>
+        <v>527522</v>
       </c>
       <c r="R59" t="n">
-        <v>7059466</v>
+        <v>7059566</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6461,32 +6461,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125598556</v>
+        <v>125598516</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>74878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527522</v>
+        <v>527519</v>
       </c>
       <c r="R60" t="n">
-        <v>7059566</v>
+        <v>7059332</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6558,32 +6558,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125598516</v>
+        <v>125598525</v>
       </c>
       <c r="B61" t="n">
-        <v>74878</v>
+        <v>80075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527519</v>
+        <v>527496</v>
       </c>
       <c r="R61" t="n">
-        <v>7059332</v>
+        <v>7059466</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598476</v>
+        <v>125598528</v>
       </c>
       <c r="B43" t="n">
-        <v>79561</v>
+        <v>80947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527488</v>
+        <v>527479</v>
       </c>
       <c r="R43" t="n">
         <v>7059420</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598528</v>
+        <v>125598476</v>
       </c>
       <c r="B44" t="n">
-        <v>80947</v>
+        <v>79561</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527479</v>
+        <v>527488</v>
       </c>
       <c r="R44" t="n">
         <v>7059420</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598481</v>
+        <v>125598468</v>
       </c>
       <c r="B33" t="n">
-        <v>91232</v>
+        <v>79590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527880</v>
+        <v>527542</v>
       </c>
       <c r="R33" t="n">
-        <v>7059774</v>
+        <v>7059620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598468</v>
+        <v>125598521</v>
       </c>
       <c r="B34" t="n">
-        <v>79590</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527542</v>
+        <v>527890</v>
       </c>
       <c r="R34" t="n">
-        <v>7059620</v>
+        <v>7059852</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598521</v>
+        <v>125598481</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>91232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527890</v>
+        <v>527880</v>
       </c>
       <c r="R35" t="n">
-        <v>7059852</v>
+        <v>7059774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598465</v>
+        <v>125598475</v>
       </c>
       <c r="B36" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528141</v>
+        <v>528015</v>
       </c>
       <c r="R36" t="n">
-        <v>7059905</v>
+        <v>7059826</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598466</v>
+        <v>125598566</v>
       </c>
       <c r="B37" t="n">
-        <v>79590</v>
+        <v>91493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527759</v>
+        <v>527975</v>
       </c>
       <c r="R37" t="n">
-        <v>7059678</v>
+        <v>7059791</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,10 +4327,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598454</v>
+        <v>125598576</v>
       </c>
       <c r="B38" t="n">
-        <v>96592</v>
+        <v>75059</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,21 +4338,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528167</v>
+        <v>527583</v>
       </c>
       <c r="R38" t="n">
-        <v>7059940</v>
+        <v>7059611</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,32 +4424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598566</v>
+        <v>125598512</v>
       </c>
       <c r="B39" t="n">
-        <v>91493</v>
+        <v>80076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527975</v>
+        <v>527496</v>
       </c>
       <c r="R39" t="n">
-        <v>7059791</v>
+        <v>7059466</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598576</v>
+        <v>125598465</v>
       </c>
       <c r="B40" t="n">
-        <v>75059</v>
+        <v>79590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527583</v>
+        <v>528141</v>
       </c>
       <c r="R40" t="n">
-        <v>7059611</v>
+        <v>7059905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598512</v>
+        <v>125598466</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527496</v>
+        <v>527759</v>
       </c>
       <c r="R41" t="n">
-        <v>7059466</v>
+        <v>7059678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598475</v>
+        <v>125598454</v>
       </c>
       <c r="B42" t="n">
-        <v>79561</v>
+        <v>96592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528015</v>
+        <v>528167</v>
       </c>
       <c r="R42" t="n">
-        <v>7059826</v>
+        <v>7059940</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598528</v>
+        <v>125598476</v>
       </c>
       <c r="B43" t="n">
-        <v>80947</v>
+        <v>79561</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527479</v>
+        <v>527488</v>
       </c>
       <c r="R43" t="n">
         <v>7059420</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598476</v>
+        <v>125598528</v>
       </c>
       <c r="B44" t="n">
-        <v>79561</v>
+        <v>80947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527488</v>
+        <v>527479</v>
       </c>
       <c r="R44" t="n">
         <v>7059420</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598455</v>
+        <v>125598520</v>
       </c>
       <c r="B50" t="n">
-        <v>96592</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527827</v>
+        <v>527925</v>
       </c>
       <c r="R50" t="n">
-        <v>7059738</v>
+        <v>7059867</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598520</v>
+        <v>125598455</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>96592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527925</v>
+        <v>527827</v>
       </c>
       <c r="R52" t="n">
-        <v>7059867</v>
+        <v>7059738</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598458</v>
+        <v>125598511</v>
       </c>
       <c r="B57" t="n">
-        <v>96592</v>
+        <v>80076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527539</v>
+        <v>527884</v>
       </c>
       <c r="R57" t="n">
-        <v>7059464</v>
+        <v>7059785</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598511</v>
+        <v>125598458</v>
       </c>
       <c r="B58" t="n">
-        <v>80076</v>
+        <v>96592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527884</v>
+        <v>527539</v>
       </c>
       <c r="R58" t="n">
-        <v>7059785</v>
+        <v>7059464</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>125584011</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>125584025</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>125583991</v>
       </c>
       <c r="B9" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>125598555</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125598557</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>125598519</v>
       </c>
       <c r="B12" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125598553</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>125598459</v>
       </c>
       <c r="B15" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>125598537</v>
       </c>
       <c r="B16" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>125598460</v>
       </c>
       <c r="B17" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>125598545</v>
       </c>
       <c r="B18" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125598510</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>125598562</v>
       </c>
       <c r="B20" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>125598526</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>125598574</v>
       </c>
       <c r="B22" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125598575</v>
       </c>
       <c r="B23" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>125598515</v>
       </c>
       <c r="B24" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598450</v>
+        <v>125598561</v>
       </c>
       <c r="B25" t="n">
-        <v>75067</v>
+        <v>82785</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527522</v>
+        <v>527520</v>
       </c>
       <c r="R25" t="n">
-        <v>7059339</v>
+        <v>7059331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598579</v>
+        <v>125598450</v>
       </c>
       <c r="B26" t="n">
-        <v>77921</v>
+        <v>75068</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527524</v>
+        <v>527522</v>
       </c>
       <c r="R26" t="n">
-        <v>7059550</v>
+        <v>7059339</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598522</v>
+        <v>125598579</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>77922</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527884</v>
+        <v>527524</v>
       </c>
       <c r="R27" t="n">
-        <v>7059787</v>
+        <v>7059550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598561</v>
+        <v>125598522</v>
       </c>
       <c r="B28" t="n">
-        <v>82784</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527520</v>
+        <v>527884</v>
       </c>
       <c r="R28" t="n">
-        <v>7059331</v>
+        <v>7059787</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598456</v>
+        <v>125598448</v>
       </c>
       <c r="B29" t="n">
-        <v>96592</v>
+        <v>75068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527574</v>
+        <v>528190</v>
       </c>
       <c r="R29" t="n">
-        <v>7059456</v>
+        <v>7059902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598448</v>
+        <v>125598456</v>
       </c>
       <c r="B30" t="n">
-        <v>75067</v>
+        <v>96594</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528190</v>
+        <v>527574</v>
       </c>
       <c r="R30" t="n">
-        <v>7059902</v>
+        <v>7059456</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
         <v>125598457</v>
       </c>
       <c r="B31" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598482</v>
+        <v>125598468</v>
       </c>
       <c r="B32" t="n">
-        <v>91232</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527578</v>
+        <v>527542</v>
       </c>
       <c r="R32" t="n">
-        <v>7059506</v>
+        <v>7059620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598468</v>
+        <v>125598482</v>
       </c>
       <c r="B33" t="n">
-        <v>79590</v>
+        <v>91234</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527542</v>
+        <v>527578</v>
       </c>
       <c r="R33" t="n">
-        <v>7059620</v>
+        <v>7059506</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598521</v>
+        <v>125598481</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>91234</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527890</v>
+        <v>527880</v>
       </c>
       <c r="R34" t="n">
-        <v>7059852</v>
+        <v>7059774</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598481</v>
+        <v>125598521</v>
       </c>
       <c r="B35" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527880</v>
+        <v>527890</v>
       </c>
       <c r="R35" t="n">
-        <v>7059774</v>
+        <v>7059852</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598475</v>
+        <v>125598454</v>
       </c>
       <c r="B36" t="n">
-        <v>79561</v>
+        <v>96594</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528015</v>
+        <v>528167</v>
       </c>
       <c r="R36" t="n">
-        <v>7059826</v>
+        <v>7059940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
         <v>125598566</v>
       </c>
       <c r="B37" t="n">
-        <v>91493</v>
+        <v>91495</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>125598576</v>
       </c>
       <c r="B38" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598512</v>
+        <v>125598465</v>
       </c>
       <c r="B39" t="n">
-        <v>80076</v>
+        <v>79591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527496</v>
+        <v>528141</v>
       </c>
       <c r="R39" t="n">
-        <v>7059466</v>
+        <v>7059905</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598465</v>
+        <v>125598466</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528141</v>
+        <v>527759</v>
       </c>
       <c r="R40" t="n">
-        <v>7059905</v>
+        <v>7059678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598466</v>
+        <v>125598512</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>80077</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527759</v>
+        <v>527496</v>
       </c>
       <c r="R41" t="n">
-        <v>7059678</v>
+        <v>7059466</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598454</v>
+        <v>125598475</v>
       </c>
       <c r="B42" t="n">
-        <v>96592</v>
+        <v>79562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528167</v>
+        <v>528015</v>
       </c>
       <c r="R42" t="n">
-        <v>7059940</v>
+        <v>7059826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598476</v>
+        <v>125598528</v>
       </c>
       <c r="B43" t="n">
-        <v>79561</v>
+        <v>80948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527488</v>
+        <v>527479</v>
       </c>
       <c r="R43" t="n">
         <v>7059420</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598528</v>
+        <v>125598535</v>
       </c>
       <c r="B44" t="n">
-        <v>80947</v>
+        <v>78731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527479</v>
+        <v>527536</v>
       </c>
       <c r="R44" t="n">
-        <v>7059420</v>
+        <v>7059461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598535</v>
+        <v>125598554</v>
       </c>
       <c r="B45" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527536</v>
+        <v>527561</v>
       </c>
       <c r="R45" t="n">
-        <v>7059461</v>
+        <v>7059318</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598554</v>
+        <v>125598467</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527561</v>
+        <v>527570</v>
       </c>
       <c r="R46" t="n">
-        <v>7059318</v>
+        <v>7059603</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598467</v>
+        <v>125598452</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>75068</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527570</v>
+        <v>527573</v>
       </c>
       <c r="R47" t="n">
-        <v>7059603</v>
+        <v>7059652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598452</v>
+        <v>125598476</v>
       </c>
       <c r="B48" t="n">
-        <v>75067</v>
+        <v>79562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527573</v>
+        <v>527488</v>
       </c>
       <c r="R48" t="n">
-        <v>7059652</v>
+        <v>7059420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
         <v>125598534</v>
       </c>
       <c r="B49" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>80077</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R50" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598509</v>
+        <v>125598520</v>
       </c>
       <c r="B51" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528048</v>
+        <v>527925</v>
       </c>
       <c r="R51" t="n">
-        <v>7059876</v>
+        <v>7059867</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5688,7 +5688,7 @@
         <v>125598455</v>
       </c>
       <c r="B52" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>125598543</v>
       </c>
       <c r="B53" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>125598451</v>
       </c>
       <c r="B54" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>125598449</v>
       </c>
       <c r="B55" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>125598536</v>
       </c>
       <c r="B56" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598511</v>
+        <v>125598458</v>
       </c>
       <c r="B57" t="n">
-        <v>80076</v>
+        <v>96594</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527884</v>
+        <v>527539</v>
       </c>
       <c r="R57" t="n">
-        <v>7059785</v>
+        <v>7059464</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598458</v>
+        <v>125598511</v>
       </c>
       <c r="B58" t="n">
-        <v>96592</v>
+        <v>80077</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527539</v>
+        <v>527884</v>
       </c>
       <c r="R58" t="n">
-        <v>7059464</v>
+        <v>7059785</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6367,7 +6367,7 @@
         <v>125598556</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>125598516</v>
       </c>
       <c r="B60" t="n">
-        <v>74878</v>
+        <v>74879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>125598525</v>
       </c>
       <c r="B61" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>125598498</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>125598499</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>125598492</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>125598489</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>125598491</v>
       </c>
       <c r="B66" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>125598490</v>
       </c>
       <c r="B67" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>125598487</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>125598500</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>125598496</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>125598488</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>125598497</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125598495</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>125598502</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>125598493</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>125598494</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598454</v>
+        <v>125598475</v>
       </c>
       <c r="B36" t="n">
-        <v>96594</v>
+        <v>79562</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528167</v>
+        <v>528015</v>
       </c>
       <c r="R36" t="n">
-        <v>7059940</v>
+        <v>7059826</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598566</v>
+        <v>125598454</v>
       </c>
       <c r="B37" t="n">
-        <v>91495</v>
+        <v>96594</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527975</v>
+        <v>528167</v>
       </c>
       <c r="R37" t="n">
-        <v>7059791</v>
+        <v>7059940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598576</v>
+        <v>125598566</v>
       </c>
       <c r="B38" t="n">
-        <v>75060</v>
+        <v>91495</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527583</v>
+        <v>527975</v>
       </c>
       <c r="R38" t="n">
-        <v>7059611</v>
+        <v>7059791</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598465</v>
+        <v>125598576</v>
       </c>
       <c r="B39" t="n">
-        <v>79591</v>
+        <v>75060</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528141</v>
+        <v>527583</v>
       </c>
       <c r="R39" t="n">
-        <v>7059905</v>
+        <v>7059611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,7 +4521,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598466</v>
+        <v>125598465</v>
       </c>
       <c r="B40" t="n">
         <v>79591</v>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527759</v>
+        <v>528141</v>
       </c>
       <c r="R40" t="n">
-        <v>7059678</v>
+        <v>7059905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598512</v>
+        <v>125598466</v>
       </c>
       <c r="B41" t="n">
-        <v>80077</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527496</v>
+        <v>527759</v>
       </c>
       <c r="R41" t="n">
-        <v>7059466</v>
+        <v>7059678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598475</v>
+        <v>125598512</v>
       </c>
       <c r="B42" t="n">
-        <v>79562</v>
+        <v>80077</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528015</v>
+        <v>527496</v>
       </c>
       <c r="R42" t="n">
-        <v>7059826</v>
+        <v>7059466</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598509</v>
+        <v>125598520</v>
       </c>
       <c r="B50" t="n">
-        <v>80077</v>
+        <v>78732</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528048</v>
+        <v>527925</v>
       </c>
       <c r="R50" t="n">
-        <v>7059876</v>
+        <v>7059867</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598520</v>
+        <v>125598455</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>96594</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527925</v>
+        <v>527827</v>
       </c>
       <c r="R51" t="n">
-        <v>7059867</v>
+        <v>7059738</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598455</v>
+        <v>125598509</v>
       </c>
       <c r="B52" t="n">
-        <v>96594</v>
+        <v>80077</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527827</v>
+        <v>528048</v>
       </c>
       <c r="R52" t="n">
-        <v>7059738</v>
+        <v>7059876</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>125598519</v>
       </c>
       <c r="B12" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>125598459</v>
       </c>
       <c r="B15" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>125598537</v>
       </c>
       <c r="B16" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>125598460</v>
       </c>
       <c r="B17" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>125598545</v>
       </c>
       <c r="B18" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>125598574</v>
       </c>
       <c r="B22" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125598575</v>
       </c>
       <c r="B23" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598450</v>
+        <v>125598579</v>
       </c>
       <c r="B26" t="n">
-        <v>75068</v>
+        <v>77922</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527522</v>
+        <v>527524</v>
       </c>
       <c r="R26" t="n">
-        <v>7059339</v>
+        <v>7059550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598579</v>
+        <v>125598450</v>
       </c>
       <c r="B27" t="n">
-        <v>77922</v>
+        <v>75068</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527524</v>
+        <v>527522</v>
       </c>
       <c r="R27" t="n">
-        <v>7059550</v>
+        <v>7059339</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598448</v>
+        <v>125598456</v>
       </c>
       <c r="B29" t="n">
-        <v>75068</v>
+        <v>96596</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528190</v>
+        <v>527574</v>
       </c>
       <c r="R29" t="n">
-        <v>7059902</v>
+        <v>7059456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598456</v>
+        <v>125598448</v>
       </c>
       <c r="B30" t="n">
-        <v>96594</v>
+        <v>75068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527574</v>
+        <v>528190</v>
       </c>
       <c r="R30" t="n">
-        <v>7059456</v>
+        <v>7059902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
         <v>125598457</v>
       </c>
       <c r="B31" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598468</v>
+        <v>125598482</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>91236</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527542</v>
+        <v>527578</v>
       </c>
       <c r="R32" t="n">
-        <v>7059620</v>
+        <v>7059506</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598482</v>
+        <v>125598468</v>
       </c>
       <c r="B33" t="n">
-        <v>91234</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527578</v>
+        <v>527542</v>
       </c>
       <c r="R33" t="n">
-        <v>7059506</v>
+        <v>7059620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,7 +3942,7 @@
         <v>125598481</v>
       </c>
       <c r="B34" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>125598454</v>
       </c>
       <c r="B37" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>125598566</v>
       </c>
       <c r="B38" t="n">
-        <v>91495</v>
+        <v>91497</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598528</v>
+        <v>125598535</v>
       </c>
       <c r="B43" t="n">
-        <v>80948</v>
+        <v>78731</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527479</v>
+        <v>527536</v>
       </c>
       <c r="R43" t="n">
-        <v>7059420</v>
+        <v>7059461</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598535</v>
+        <v>125598554</v>
       </c>
       <c r="B44" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527536</v>
+        <v>527561</v>
       </c>
       <c r="R44" t="n">
-        <v>7059461</v>
+        <v>7059318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598554</v>
+        <v>125598467</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527561</v>
+        <v>527570</v>
       </c>
       <c r="R45" t="n">
-        <v>7059318</v>
+        <v>7059603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598467</v>
+        <v>125598528</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>80948</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527570</v>
+        <v>527479</v>
       </c>
       <c r="R46" t="n">
-        <v>7059603</v>
+        <v>7059420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B50" t="n">
-        <v>78732</v>
+        <v>80077</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R50" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598455</v>
+        <v>125598520</v>
       </c>
       <c r="B51" t="n">
-        <v>96594</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527827</v>
+        <v>527925</v>
       </c>
       <c r="R51" t="n">
-        <v>7059738</v>
+        <v>7059867</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598509</v>
+        <v>125598455</v>
       </c>
       <c r="B52" t="n">
-        <v>80077</v>
+        <v>96596</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528048</v>
+        <v>527827</v>
       </c>
       <c r="R52" t="n">
-        <v>7059876</v>
+        <v>7059738</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5782,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125598543</v>
+        <v>125598451</v>
       </c>
       <c r="B53" t="n">
-        <v>91395</v>
+        <v>75068</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527509</v>
+        <v>527552</v>
       </c>
       <c r="R53" t="n">
-        <v>7059455</v>
+        <v>7059543</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598451</v>
+        <v>125598543</v>
       </c>
       <c r="B54" t="n">
-        <v>75068</v>
+        <v>91397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527552</v>
+        <v>527509</v>
       </c>
       <c r="R54" t="n">
-        <v>7059543</v>
+        <v>7059455</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125598458</v>
+        <v>125598511</v>
       </c>
       <c r="B57" t="n">
-        <v>96594</v>
+        <v>80077</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527539</v>
+        <v>527884</v>
       </c>
       <c r="R57" t="n">
-        <v>7059464</v>
+        <v>7059785</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125598511</v>
+        <v>125598458</v>
       </c>
       <c r="B58" t="n">
-        <v>80077</v>
+        <v>96596</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527884</v>
+        <v>527539</v>
       </c>
       <c r="R58" t="n">
-        <v>7059785</v>
+        <v>7059464</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125598487</v>
+        <v>125598500</v>
       </c>
       <c r="B68" t="n">
         <v>57652</v>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>528055</v>
+        <v>527614</v>
       </c>
       <c r="R68" t="n">
-        <v>7059900</v>
+        <v>7059597</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7369,7 +7369,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125598500</v>
+        <v>125598487</v>
       </c>
       <c r="B69" t="n">
         <v>57652</v>
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527614</v>
+        <v>528055</v>
       </c>
       <c r="R69" t="n">
-        <v>7059597</v>
+        <v>7059900</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598475</v>
+        <v>125598454</v>
       </c>
       <c r="B36" t="n">
-        <v>79562</v>
+        <v>96596</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528015</v>
+        <v>528167</v>
       </c>
       <c r="R36" t="n">
-        <v>7059826</v>
+        <v>7059940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598454</v>
+        <v>125598566</v>
       </c>
       <c r="B37" t="n">
-        <v>96596</v>
+        <v>91497</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528167</v>
+        <v>527975</v>
       </c>
       <c r="R37" t="n">
-        <v>7059940</v>
+        <v>7059791</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598566</v>
+        <v>125598576</v>
       </c>
       <c r="B38" t="n">
-        <v>91497</v>
+        <v>75060</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527975</v>
+        <v>527583</v>
       </c>
       <c r="R38" t="n">
-        <v>7059791</v>
+        <v>7059611</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598576</v>
+        <v>125598465</v>
       </c>
       <c r="B39" t="n">
-        <v>75060</v>
+        <v>79591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527583</v>
+        <v>528141</v>
       </c>
       <c r="R39" t="n">
-        <v>7059611</v>
+        <v>7059905</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,7 +4521,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598465</v>
+        <v>125598466</v>
       </c>
       <c r="B40" t="n">
         <v>79591</v>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528141</v>
+        <v>527759</v>
       </c>
       <c r="R40" t="n">
-        <v>7059905</v>
+        <v>7059678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598466</v>
+        <v>125598512</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>80077</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527759</v>
+        <v>527496</v>
       </c>
       <c r="R41" t="n">
-        <v>7059678</v>
+        <v>7059466</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598512</v>
+        <v>125598475</v>
       </c>
       <c r="B42" t="n">
-        <v>80077</v>
+        <v>79562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527496</v>
+        <v>528015</v>
       </c>
       <c r="R42" t="n">
-        <v>7059466</v>
+        <v>7059826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125598509</v>
+        <v>125598455</v>
       </c>
       <c r="B50" t="n">
-        <v>80077</v>
+        <v>96596</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,21 +5502,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528048</v>
+        <v>527827</v>
       </c>
       <c r="R50" t="n">
-        <v>7059876</v>
+        <v>7059738</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>80077</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R51" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598455</v>
+        <v>125598520</v>
       </c>
       <c r="B52" t="n">
-        <v>96596</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527827</v>
+        <v>527925</v>
       </c>
       <c r="R52" t="n">
-        <v>7059738</v>
+        <v>7059867</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125598500</v>
+        <v>125598487</v>
       </c>
       <c r="B68" t="n">
         <v>57652</v>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527614</v>
+        <v>528055</v>
       </c>
       <c r="R68" t="n">
-        <v>7059597</v>
+        <v>7059900</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7369,7 +7369,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125598487</v>
+        <v>125598500</v>
       </c>
       <c r="B69" t="n">
         <v>57652</v>
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528055</v>
+        <v>527614</v>
       </c>
       <c r="R69" t="n">
-        <v>7059900</v>
+        <v>7059597</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>125598519</v>
       </c>
       <c r="B12" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125598461</v>
       </c>
       <c r="B14" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125598459</v>
+        <v>125598537</v>
       </c>
       <c r="B15" t="n">
-        <v>96596</v>
+        <v>91399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527589</v>
+        <v>528146</v>
       </c>
       <c r="R15" t="n">
-        <v>7059511</v>
+        <v>7059953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598537</v>
+        <v>125598459</v>
       </c>
       <c r="B16" t="n">
-        <v>91397</v>
+        <v>96598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528146</v>
+        <v>527589</v>
       </c>
       <c r="R16" t="n">
-        <v>7059953</v>
+        <v>7059511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598460</v>
+        <v>125598545</v>
       </c>
       <c r="B17" t="n">
-        <v>96596</v>
+        <v>91399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527527</v>
+        <v>527569</v>
       </c>
       <c r="R17" t="n">
-        <v>7059584</v>
+        <v>7059499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125598545</v>
+        <v>125598460</v>
       </c>
       <c r="B18" t="n">
-        <v>91397</v>
+        <v>96598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527569</v>
+        <v>527527</v>
       </c>
       <c r="R18" t="n">
-        <v>7059499</v>
+        <v>7059584</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125598562</v>
+        <v>125598526</v>
       </c>
       <c r="B20" t="n">
-        <v>82785</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527573</v>
+        <v>527563</v>
       </c>
       <c r="R20" t="n">
-        <v>7059654</v>
+        <v>7059540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598526</v>
+        <v>125598562</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>82785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527563</v>
+        <v>527573</v>
       </c>
       <c r="R21" t="n">
-        <v>7059540</v>
+        <v>7059654</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
         <v>125598574</v>
       </c>
       <c r="B22" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>125598575</v>
       </c>
       <c r="B23" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125598561</v>
+        <v>125598579</v>
       </c>
       <c r="B25" t="n">
-        <v>82785</v>
+        <v>77922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527520</v>
+        <v>527524</v>
       </c>
       <c r="R25" t="n">
-        <v>7059331</v>
+        <v>7059550</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598579</v>
+        <v>125598450</v>
       </c>
       <c r="B26" t="n">
-        <v>77922</v>
+        <v>75068</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527524</v>
+        <v>527522</v>
       </c>
       <c r="R26" t="n">
-        <v>7059550</v>
+        <v>7059339</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598450</v>
+        <v>125598522</v>
       </c>
       <c r="B27" t="n">
-        <v>75068</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527522</v>
+        <v>527884</v>
       </c>
       <c r="R27" t="n">
-        <v>7059339</v>
+        <v>7059787</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125598522</v>
+        <v>125598561</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>82785</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527884</v>
+        <v>527520</v>
       </c>
       <c r="R28" t="n">
-        <v>7059787</v>
+        <v>7059331</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>125598456</v>
       </c>
       <c r="B29" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598457</v>
+        <v>125598468</v>
       </c>
       <c r="B31" t="n">
-        <v>96596</v>
+        <v>79591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3686,7 +3686,7 @@
         <v>527542</v>
       </c>
       <c r="R31" t="n">
-        <v>7059349</v>
+        <v>7059620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598482</v>
+        <v>125598521</v>
       </c>
       <c r="B32" t="n">
-        <v>91236</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527578</v>
+        <v>527890</v>
       </c>
       <c r="R32" t="n">
-        <v>7059506</v>
+        <v>7059852</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598468</v>
+        <v>125598457</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>96598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
         <v>527542</v>
       </c>
       <c r="R33" t="n">
-        <v>7059620</v>
+        <v>7059349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598481</v>
+        <v>125598482</v>
       </c>
       <c r="B34" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527880</v>
+        <v>527578</v>
       </c>
       <c r="R34" t="n">
-        <v>7059774</v>
+        <v>7059506</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598521</v>
+        <v>125598481</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>91238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527890</v>
+        <v>527880</v>
       </c>
       <c r="R35" t="n">
-        <v>7059852</v>
+        <v>7059774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598454</v>
+        <v>125598465</v>
       </c>
       <c r="B36" t="n">
-        <v>96596</v>
+        <v>79591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528167</v>
+        <v>528141</v>
       </c>
       <c r="R36" t="n">
-        <v>7059940</v>
+        <v>7059905</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598566</v>
+        <v>125598576</v>
       </c>
       <c r="B37" t="n">
-        <v>91497</v>
+        <v>75060</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527975</v>
+        <v>527583</v>
       </c>
       <c r="R37" t="n">
-        <v>7059791</v>
+        <v>7059611</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598576</v>
+        <v>125598566</v>
       </c>
       <c r="B38" t="n">
-        <v>75060</v>
+        <v>91499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527583</v>
+        <v>527975</v>
       </c>
       <c r="R38" t="n">
-        <v>7059611</v>
+        <v>7059791</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598465</v>
+        <v>125598512</v>
       </c>
       <c r="B39" t="n">
-        <v>79591</v>
+        <v>80077</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528141</v>
+        <v>527496</v>
       </c>
       <c r="R39" t="n">
-        <v>7059905</v>
+        <v>7059466</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598466</v>
+        <v>125598454</v>
       </c>
       <c r="B40" t="n">
-        <v>79591</v>
+        <v>96598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527759</v>
+        <v>528167</v>
       </c>
       <c r="R40" t="n">
-        <v>7059678</v>
+        <v>7059940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598512</v>
+        <v>125598466</v>
       </c>
       <c r="B41" t="n">
-        <v>80077</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527496</v>
+        <v>527759</v>
       </c>
       <c r="R41" t="n">
-        <v>7059466</v>
+        <v>7059678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598535</v>
+        <v>125598476</v>
       </c>
       <c r="B43" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527536</v>
+        <v>527488</v>
       </c>
       <c r="R43" t="n">
-        <v>7059461</v>
+        <v>7059420</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598554</v>
+        <v>125598535</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527561</v>
+        <v>527536</v>
       </c>
       <c r="R44" t="n">
-        <v>7059318</v>
+        <v>7059461</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598467</v>
+        <v>125598554</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527570</v>
+        <v>527561</v>
       </c>
       <c r="R45" t="n">
-        <v>7059603</v>
+        <v>7059318</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598528</v>
+        <v>125598467</v>
       </c>
       <c r="B46" t="n">
-        <v>80948</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527479</v>
+        <v>527570</v>
       </c>
       <c r="R46" t="n">
-        <v>7059420</v>
+        <v>7059603</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598476</v>
+        <v>125598528</v>
       </c>
       <c r="B48" t="n">
-        <v>79562</v>
+        <v>80948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527488</v>
+        <v>527479</v>
       </c>
       <c r="R48" t="n">
         <v>7059420</v>
@@ -5494,7 +5494,7 @@
         <v>125598455</v>
       </c>
       <c r="B50" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125598509</v>
+        <v>125598520</v>
       </c>
       <c r="B51" t="n">
-        <v>80077</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528048</v>
+        <v>527925</v>
       </c>
       <c r="R51" t="n">
-        <v>7059876</v>
+        <v>7059867</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125598520</v>
+        <v>125598509</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>80077</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527925</v>
+        <v>528048</v>
       </c>
       <c r="R52" t="n">
-        <v>7059867</v>
+        <v>7059876</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125598543</v>
+        <v>125598449</v>
       </c>
       <c r="B54" t="n">
-        <v>91397</v>
+        <v>75068</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527509</v>
+        <v>528035</v>
       </c>
       <c r="R54" t="n">
-        <v>7059455</v>
+        <v>7059829</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5976,10 +5976,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125598449</v>
+        <v>125598536</v>
       </c>
       <c r="B55" t="n">
-        <v>75068</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528035</v>
+        <v>527559</v>
       </c>
       <c r="R55" t="n">
-        <v>7059829</v>
+        <v>7059578</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6073,32 +6073,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125598536</v>
+        <v>125598543</v>
       </c>
       <c r="B56" t="n">
-        <v>78731</v>
+        <v>91399</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527559</v>
+        <v>527509</v>
       </c>
       <c r="R56" t="n">
-        <v>7059578</v>
+        <v>7059455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6270,7 +6270,7 @@
         <v>125598458</v>
       </c>
       <c r="B58" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125598456</v>
+        <v>125598448</v>
       </c>
       <c r="B29" t="n">
-        <v>96598</v>
+        <v>75068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527574</v>
+        <v>528190</v>
       </c>
       <c r="R29" t="n">
-        <v>7059456</v>
+        <v>7059902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125598448</v>
+        <v>125598456</v>
       </c>
       <c r="B30" t="n">
-        <v>75068</v>
+        <v>96598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528190</v>
+        <v>527574</v>
       </c>
       <c r="R30" t="n">
-        <v>7059902</v>
+        <v>7059456</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125598468</v>
+        <v>125598457</v>
       </c>
       <c r="B31" t="n">
-        <v>79591</v>
+        <v>96598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3686,7 +3686,7 @@
         <v>527542</v>
       </c>
       <c r="R31" t="n">
-        <v>7059620</v>
+        <v>7059349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125598521</v>
+        <v>125598482</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>91238</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527890</v>
+        <v>527578</v>
       </c>
       <c r="R32" t="n">
-        <v>7059852</v>
+        <v>7059506</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125598457</v>
+        <v>125598481</v>
       </c>
       <c r="B33" t="n">
-        <v>96598</v>
+        <v>91238</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527542</v>
+        <v>527880</v>
       </c>
       <c r="R33" t="n">
-        <v>7059349</v>
+        <v>7059774</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125598482</v>
+        <v>125598468</v>
       </c>
       <c r="B34" t="n">
-        <v>91238</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527578</v>
+        <v>527542</v>
       </c>
       <c r="R34" t="n">
-        <v>7059506</v>
+        <v>7059620</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125598481</v>
+        <v>125598521</v>
       </c>
       <c r="B35" t="n">
-        <v>91238</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527880</v>
+        <v>527890</v>
       </c>
       <c r="R35" t="n">
-        <v>7059774</v>
+        <v>7059852</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125598465</v>
+        <v>125598576</v>
       </c>
       <c r="B36" t="n">
-        <v>79591</v>
+        <v>75060</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528141</v>
+        <v>527583</v>
       </c>
       <c r="R36" t="n">
-        <v>7059905</v>
+        <v>7059611</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,32 +4230,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125598576</v>
+        <v>125598566</v>
       </c>
       <c r="B37" t="n">
-        <v>75060</v>
+        <v>91499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527583</v>
+        <v>527975</v>
       </c>
       <c r="R37" t="n">
-        <v>7059611</v>
+        <v>7059791</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125598566</v>
+        <v>125598512</v>
       </c>
       <c r="B38" t="n">
-        <v>91499</v>
+        <v>80077</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527975</v>
+        <v>527496</v>
       </c>
       <c r="R38" t="n">
-        <v>7059791</v>
+        <v>7059466</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4424,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125598512</v>
+        <v>125598454</v>
       </c>
       <c r="B39" t="n">
-        <v>80077</v>
+        <v>96598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527496</v>
+        <v>528167</v>
       </c>
       <c r="R39" t="n">
-        <v>7059466</v>
+        <v>7059940</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125598454</v>
+        <v>125598475</v>
       </c>
       <c r="B40" t="n">
-        <v>96598</v>
+        <v>79562</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528167</v>
+        <v>528015</v>
       </c>
       <c r="R40" t="n">
-        <v>7059940</v>
+        <v>7059826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125598466</v>
+        <v>125598465</v>
       </c>
       <c r="B41" t="n">
         <v>79591</v>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527759</v>
+        <v>528141</v>
       </c>
       <c r="R41" t="n">
-        <v>7059678</v>
+        <v>7059905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125598475</v>
+        <v>125598466</v>
       </c>
       <c r="B42" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528015</v>
+        <v>527759</v>
       </c>
       <c r="R42" t="n">
-        <v>7059826</v>
+        <v>7059678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125598476</v>
+        <v>125598535</v>
       </c>
       <c r="B43" t="n">
-        <v>79562</v>
+        <v>78731</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527488</v>
+        <v>527536</v>
       </c>
       <c r="R43" t="n">
-        <v>7059420</v>
+        <v>7059461</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125598535</v>
+        <v>125598554</v>
       </c>
       <c r="B44" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527536</v>
+        <v>527561</v>
       </c>
       <c r="R44" t="n">
-        <v>7059461</v>
+        <v>7059318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125598554</v>
+        <v>125598467</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527561</v>
+        <v>527570</v>
       </c>
       <c r="R45" t="n">
-        <v>7059318</v>
+        <v>7059603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125598467</v>
+        <v>125598452</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>75068</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,21 +5114,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527570</v>
+        <v>527573</v>
       </c>
       <c r="R46" t="n">
-        <v>7059603</v>
+        <v>7059652</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125598452</v>
+        <v>125598528</v>
       </c>
       <c r="B47" t="n">
-        <v>75068</v>
+        <v>80948</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527573</v>
+        <v>527479</v>
       </c>
       <c r="R47" t="n">
-        <v>7059652</v>
+        <v>7059420</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125598528</v>
+        <v>125598476</v>
       </c>
       <c r="B48" t="n">
-        <v>80948</v>
+        <v>79562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527479</v>
+        <v>527488</v>
       </c>
       <c r="R48" t="n">
         <v>7059420</v>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -6658,7 +6658,7 @@
         <v>125598498</v>
       </c>
       <c r="B62" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>125598499</v>
       </c>
       <c r="B63" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>125598492</v>
       </c>
       <c r="B64" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>125598489</v>
       </c>
       <c r="B65" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>125598491</v>
       </c>
       <c r="B66" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>125598490</v>
       </c>
       <c r="B67" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>125598487</v>
       </c>
       <c r="B68" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>125598500</v>
       </c>
       <c r="B69" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>125598496</v>
       </c>
       <c r="B70" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>125598488</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>125598497</v>
       </c>
       <c r="B72" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125598495</v>
       </c>
       <c r="B73" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>125598502</v>
       </c>
       <c r="B74" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>125598493</v>
       </c>
       <c r="B75" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>125598494</v>
       </c>
       <c r="B76" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 19604-2025 artfynd.xlsx
+++ b/artfynd/A 19604-2025 artfynd.xlsx
@@ -6658,7 +6658,7 @@
         <v>125598498</v>
       </c>
       <c r="B62" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>125598499</v>
       </c>
       <c r="B63" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>125598492</v>
       </c>
       <c r="B64" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>125598489</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>125598491</v>
       </c>
       <c r="B66" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>125598490</v>
       </c>
       <c r="B67" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>125598487</v>
       </c>
       <c r="B68" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>125598500</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>125598496</v>
       </c>
       <c r="B70" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>125598488</v>
       </c>
       <c r="B71" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>125598497</v>
       </c>
       <c r="B72" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>125598495</v>
       </c>
       <c r="B73" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>125598502</v>
       </c>
       <c r="B74" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>125598493</v>
       </c>
       <c r="B75" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>125598494</v>
       </c>
       <c r="B76" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
